--- a/sales_report.xlsx
+++ b/sales_report.xlsx
@@ -465,7 +465,7 @@
     </row>
     <row r="3">
       <c r="B3" s="1" t="n">
-        <v>46163</v>
+        <v>46171</v>
       </c>
     </row>
     <row r="4">
@@ -503,10 +503,10 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E6" t="n">
-        <v>0.7142857142857143</v>
+        <v>0.8095238095238095</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -571,10 +571,6 @@
           <t>Mon Of</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
       <c r="J9" t="inlineStr">
         <is>
           <t>MTD</t>
@@ -664,7 +660,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>195000</v>
+        <v>210425.58</v>
       </c>
       <c r="D14" t="n">
         <v>267000</v>
@@ -695,7 +691,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>185000</v>
+        <v>212353.76</v>
       </c>
       <c r="D15" t="n">
         <v>235000</v>
@@ -726,7 +722,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>245000</v>
+        <v>271921.49</v>
       </c>
       <c r="D16" t="n">
         <v>370000</v>
@@ -757,7 +753,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>8200</v>
+        <v>8707.959999999999</v>
       </c>
       <c r="D17" t="n">
         <v>10000</v>
@@ -788,7 +784,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>9500</v>
+        <v>10432.84</v>
       </c>
       <c r="D18" t="n">
         <v>7500</v>
@@ -819,7 +815,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>105000</v>
+        <v>112927.37</v>
       </c>
       <c r="D19" t="n">
         <v>32000</v>
@@ -850,7 +846,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>7100</v>
+        <v>8128.81</v>
       </c>
       <c r="D20" t="n">
         <v>18000</v>
@@ -881,7 +877,7 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>42000</v>
+        <v>44635.09</v>
       </c>
       <c r="D21" t="n">
         <v>101000</v>
@@ -912,7 +908,7 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>41000</v>
+        <v>44607.56</v>
       </c>
       <c r="D22" t="n">
         <v>51000</v>
@@ -971,31 +967,34 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>867800</v>
+        <v>925000</v>
       </c>
       <c r="D30" t="n">
-        <v>1119500</v>
+        <v>1090000</v>
       </c>
       <c r="E30" t="n">
         <v>1479422</v>
       </c>
       <c r="F30" t="n">
-        <v>0.5865804347914253</v>
+        <v>0.625</v>
       </c>
       <c r="G30" t="n">
-        <v>1214920</v>
+        <v>1295000</v>
       </c>
       <c r="H30" t="n">
-        <v>0.8212126087079954</v>
+        <v>0.875</v>
       </c>
       <c r="L30" t="n">
-        <v>1420000</v>
+        <v>1380000</v>
       </c>
       <c r="N30" t="n">
-        <v>5063000</v>
+        <v>5250000</v>
       </c>
       <c r="O30" t="n">
-        <v>5657500</v>
+        <v>5254474</v>
+      </c>
+      <c r="R30" t="n">
+        <v>15968852</v>
       </c>
     </row>
     <row r="33">
@@ -1298,22 +1297,22 @@
         </is>
       </c>
       <c r="J45" t="n">
-        <v>617000</v>
+        <v>680000</v>
       </c>
       <c r="K45" t="n">
-        <v>1618000</v>
+        <v>1617138</v>
       </c>
       <c r="L45" t="n">
-        <v>0.3813349814585908</v>
+        <v>0.42</v>
       </c>
       <c r="P45" t="n">
-        <v>4590000</v>
+        <v>4750000</v>
       </c>
       <c r="Q45" t="n">
-        <v>6800000</v>
+        <v>6713948</v>
       </c>
       <c r="R45" t="n">
-        <v>0.675</v>
+        <v>0.708</v>
       </c>
     </row>
   </sheetData>

--- a/sales_report.xlsx
+++ b/sales_report.xlsx
@@ -503,10 +503,10 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="E6" t="n">
-        <v>0.8095238095238095</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -660,7 +660,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>210425.58</v>
+        <v>181087.26</v>
       </c>
       <c r="D14" t="n">
         <v>267000</v>
@@ -691,7 +691,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>212353.76</v>
+        <v>171119.26</v>
       </c>
       <c r="D15" t="n">
         <v>235000</v>
@@ -722,7 +722,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>271921.49</v>
+        <v>216959.88</v>
       </c>
       <c r="D16" t="n">
         <v>370000</v>
@@ -753,7 +753,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>8707.959999999999</v>
+        <v>7786.48</v>
       </c>
       <c r="D17" t="n">
         <v>10000</v>
@@ -784,7 +784,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>10432.84</v>
+        <v>8811</v>
       </c>
       <c r="D18" t="n">
         <v>7500</v>
@@ -815,7 +815,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>112927.37</v>
+        <v>94473.3</v>
       </c>
       <c r="D19" t="n">
         <v>32000</v>
@@ -846,7 +846,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>8128.81</v>
+        <v>6272.41</v>
       </c>
       <c r="D20" t="n">
         <v>18000</v>
@@ -877,7 +877,7 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>44635.09</v>
+        <v>38820.47</v>
       </c>
       <c r="D21" t="n">
         <v>101000</v>
@@ -908,7 +908,7 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>44607.56</v>
+        <v>38885.21</v>
       </c>
       <c r="D22" t="n">
         <v>51000</v>
@@ -967,7 +967,7 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>925000</v>
+        <v>780000</v>
       </c>
       <c r="D30" t="n">
         <v>1090000</v>
@@ -976,19 +976,19 @@
         <v>1479422</v>
       </c>
       <c r="F30" t="n">
-        <v>0.625</v>
+        <v>0.527</v>
       </c>
       <c r="G30" t="n">
-        <v>1295000</v>
+        <v>1092000</v>
       </c>
       <c r="H30" t="n">
-        <v>0.875</v>
+        <v>0.738</v>
       </c>
       <c r="L30" t="n">
-        <v>1380000</v>
+        <v>1520000</v>
       </c>
       <c r="N30" t="n">
-        <v>5250000</v>
+        <v>4950000</v>
       </c>
       <c r="O30" t="n">
         <v>5254474</v>
@@ -1297,22 +1297,22 @@
         </is>
       </c>
       <c r="J45" t="n">
-        <v>680000</v>
+        <v>540000</v>
       </c>
       <c r="K45" t="n">
         <v>1617138</v>
       </c>
       <c r="L45" t="n">
-        <v>0.42</v>
+        <v>0.334</v>
       </c>
       <c r="P45" t="n">
-        <v>4750000</v>
+        <v>4320000</v>
       </c>
       <c r="Q45" t="n">
         <v>6713948</v>
       </c>
       <c r="R45" t="n">
-        <v>0.708</v>
+        <v>0.643</v>
       </c>
     </row>
   </sheetData>

--- a/sales_report.xlsx
+++ b/sales_report.xlsx
@@ -9,35 +9,6 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DASHBOARD" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="REVENUE" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FORECAST" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PRODUCT2" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DAILYORDERS" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BACKLOG" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BYREPBYSTATE" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BY PRODUCT" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MTDbyORDER" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BY CUSTOMER" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BACKLOG_info" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BY GROUP" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BY ITEM-FP" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="REVENUE-DIRECT" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="REVENUE_INPUT" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BY ITEM-PAV" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BY TYPE" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SALESPERSON" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BY DISTRIBUTOR" sheetId="19" state="visible" r:id="rId19"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FIREPLACE" sheetId="20" state="visible" r:id="rId20"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PAVERS" sheetId="21" state="visible" r:id="rId21"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SWD" sheetId="22" state="visible" r:id="rId22"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OTHER" sheetId="23" state="visible" r:id="rId23"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FLOORING" sheetId="24" state="visible" r:id="rId24"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="INSTALL" sheetId="25" state="visible" r:id="rId25"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DETAIL_ALL" sheetId="26" state="visible" r:id="rId26"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FIREPLACE (2)" sheetId="27" state="visible" r:id="rId27"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BACKLOG_INPUT" sheetId="28" state="visible" r:id="rId28"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CUSTOMER" sheetId="29" state="visible" r:id="rId29"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NOTE" sheetId="30" state="visible" r:id="rId30"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ITEM" sheetId="31" state="visible" r:id="rId31"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -446,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:U45"/>
+  <dimension ref="B1:S46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -465,7 +436,7 @@
     </row>
     <row r="3">
       <c r="B3" s="1" t="n">
-        <v>46171</v>
+        <v>46163</v>
       </c>
     </row>
     <row r="4">
@@ -503,10 +474,10 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E6" t="n">
-        <v>0.8095238095238095</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -538,118 +509,126 @@
         <v>154</v>
       </c>
     </row>
-    <row r="8">
-      <c r="C8" t="inlineStr">
+    <row r="11">
+      <c r="C11" t="inlineStr">
         <is>
           <t>SALES ORDERS - CURRENT MONTH</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="J11" t="inlineStr">
         <is>
           <t>REVENUE</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="L11" t="inlineStr">
         <is>
           <t>BACKLOG</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="N11" t="inlineStr">
         <is>
           <t>SALES ORDERS - YTD</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="C9" t="inlineStr">
+    <row r="12">
+      <c r="C12" t="inlineStr">
         <is>
           <t>MTD</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>Mon Of</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
+      <c r="J12" t="inlineStr">
         <is>
           <t>MTD</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr">
+      <c r="N12" t="inlineStr">
         <is>
           <t>Current Year</t>
         </is>
       </c>
-    </row>
-    <row r="10">
-      <c r="C10" s="1" t="n">
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>Prior Year</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>Quota</t>
+        </is>
+      </c>
+      <c r="S12" t="n">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="C13" s="1" t="n">
         <v>46173</v>
       </c>
-      <c r="D10" s="1" t="n">
+      <c r="D13" s="1" t="n">
         <v>45808</v>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E13" t="inlineStr">
         <is>
           <t>Quota</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="F13" t="inlineStr">
         <is>
           <t>% Quota</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="G13" t="inlineStr">
         <is>
           <t>Forecast</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
+      <c r="H13" t="inlineStr">
         <is>
           <t>% Quota</t>
         </is>
       </c>
-      <c r="J10" s="1" t="n">
+      <c r="J13" s="1" t="n">
         <v>46173</v>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="L13" t="inlineStr">
         <is>
           <t>BALANCE</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
+      <c r="N13" t="inlineStr">
         <is>
           <t>YTD</t>
         </is>
       </c>
-      <c r="O10" t="inlineStr">
+      <c r="O13" t="inlineStr">
         <is>
           <t>YTD</t>
         </is>
       </c>
-      <c r="P10" t="inlineStr">
+      <c r="P13" t="inlineStr">
         <is>
           <t>% PY</t>
         </is>
       </c>
-      <c r="R10" t="inlineStr">
+      <c r="Q13" t="inlineStr">
         <is>
           <t>YTD</t>
         </is>
       </c>
-      <c r="S10" t="inlineStr">
+      <c r="R13" t="inlineStr">
         <is>
           <t>% Quota Trend</t>
         </is>
       </c>
-      <c r="T10" t="inlineStr">
+      <c r="S13" t="inlineStr">
         <is>
           <t>Annual Quota</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>% Quota</t>
         </is>
       </c>
     </row>
@@ -660,27 +639,45 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>210425.58</v>
+        <v>203881.14</v>
       </c>
       <c r="D14" t="n">
-        <v>267000</v>
+        <v>267482.78</v>
       </c>
       <c r="E14" t="n">
         <v>352500</v>
       </c>
       <c r="F14" t="n">
-        <v>0.5531914893617021</v>
+        <v>0.5783862127659575</v>
       </c>
       <c r="G14" t="n">
-        <v>273000</v>
+        <v>285433.596</v>
       </c>
       <c r="H14" t="n">
-        <v>0.774468085106383</v>
+        <v>0.8097406978723405</v>
+      </c>
+      <c r="J14" t="n">
+        <v>135546.3</v>
+      </c>
+      <c r="L14" t="n">
+        <v>453038.5399999997</v>
       </c>
       <c r="N14" t="n">
-        <v>1080000</v>
-      </c>
-      <c r="T14" t="n">
+        <v>1119347.93</v>
+      </c>
+      <c r="O14" t="n">
+        <v>1027472.71</v>
+      </c>
+      <c r="P14" t="n">
+        <v>1.089418647430548</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>1377952.755905512</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0.8123267834857143</v>
+      </c>
+      <c r="S14" t="n">
         <v>3500000</v>
       </c>
     </row>
@@ -691,27 +688,45 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>212353.76</v>
+        <v>173446.83</v>
       </c>
       <c r="D15" t="n">
-        <v>235000</v>
+        <v>232668.87</v>
       </c>
       <c r="E15" t="n">
         <v>253000</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7312252964426877</v>
+        <v>0.6855605928853755</v>
       </c>
       <c r="G15" t="n">
-        <v>259000</v>
+        <v>242825.562</v>
       </c>
       <c r="H15" t="n">
-        <v>1.023715415019763</v>
+        <v>0.9597848300395259</v>
+      </c>
+      <c r="J15" t="n">
+        <v>86191.32999999996</v>
+      </c>
+      <c r="L15" t="n">
+        <v>343414.89</v>
       </c>
       <c r="N15" t="n">
-        <v>1150000</v>
-      </c>
-      <c r="T15" t="n">
+        <v>1126113.49</v>
+      </c>
+      <c r="O15" t="n">
+        <v>1012533.76</v>
+      </c>
+      <c r="P15" t="n">
+        <v>1.112173770877526</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>1010236.220472441</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1.114703142868277</v>
+      </c>
+      <c r="S15" t="n">
         <v>2566000</v>
       </c>
     </row>
@@ -722,27 +737,45 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>271921.49</v>
+        <v>234020.21</v>
       </c>
       <c r="D16" t="n">
-        <v>370000</v>
+        <v>365540.12</v>
       </c>
       <c r="E16" t="n">
         <v>406000</v>
       </c>
       <c r="F16" t="n">
-        <v>0.603448275862069</v>
+        <v>0.5764044581280788</v>
       </c>
       <c r="G16" t="n">
-        <v>343000</v>
+        <v>327628.2940000001</v>
       </c>
       <c r="H16" t="n">
-        <v>0.8448275862068966</v>
+        <v>0.8069662413793105</v>
+      </c>
+      <c r="J16" t="n">
+        <v>220975.64</v>
+      </c>
+      <c r="L16" t="n">
+        <v>291565.36</v>
       </c>
       <c r="N16" t="n">
-        <v>1500000</v>
-      </c>
-      <c r="T16" t="n">
+        <v>1533379.040000001</v>
+      </c>
+      <c r="O16" t="n">
+        <v>1772306.06</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0.8651886232336194</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>1780314.960629921</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0.8612964974789918</v>
+      </c>
+      <c r="S16" t="n">
         <v>4522000</v>
       </c>
     </row>
@@ -753,27 +786,45 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>8707.959999999999</v>
+        <v>7664.599999999999</v>
       </c>
       <c r="D17" t="n">
-        <v>10000</v>
+        <v>10260.86</v>
       </c>
       <c r="E17" t="n">
         <v>35000</v>
       </c>
       <c r="F17" t="n">
-        <v>0.2342857142857143</v>
+        <v>0.2189885714285714</v>
       </c>
       <c r="G17" t="n">
-        <v>11480</v>
+        <v>10730.44</v>
       </c>
       <c r="H17" t="n">
-        <v>0.328</v>
+        <v>0.306584</v>
+      </c>
+      <c r="J17" t="n">
+        <v>11430.6</v>
+      </c>
+      <c r="L17" t="n">
+        <v>16544.12</v>
       </c>
       <c r="N17" t="n">
-        <v>48000</v>
-      </c>
-      <c r="T17" t="n">
+        <v>51293.38</v>
+      </c>
+      <c r="O17" t="n">
+        <v>68651.59</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0.7471550185509177</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>440944.8818897638</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0.1163260582142857</v>
+      </c>
+      <c r="S17" t="n">
         <v>1120000</v>
       </c>
     </row>
@@ -784,27 +835,45 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>10432.84</v>
+        <v>8835.190000000001</v>
       </c>
       <c r="D18" t="n">
-        <v>7500</v>
+        <v>7625.219999999999</v>
       </c>
       <c r="E18" t="n">
         <v>65000</v>
       </c>
       <c r="F18" t="n">
-        <v>0.1461538461538462</v>
+        <v>0.135926</v>
       </c>
       <c r="G18" t="n">
-        <v>13300</v>
+        <v>12369.266</v>
       </c>
       <c r="H18" t="n">
-        <v>0.2046153846153846</v>
+        <v>0.1902964</v>
+      </c>
+      <c r="J18" t="n">
+        <v>8377.780000000001</v>
+      </c>
+      <c r="L18" t="n">
+        <v>20235.14</v>
       </c>
       <c r="N18" t="n">
-        <v>155000</v>
-      </c>
-      <c r="T18" t="n">
+        <v>146695.63</v>
+      </c>
+      <c r="O18" t="n">
+        <v>159547.65</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0.919447136952503</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>236220.4724409449</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0.6210115003333333</v>
+      </c>
+      <c r="S18" t="n">
         <v>600000</v>
       </c>
     </row>
@@ -815,27 +884,45 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>112927.37</v>
+        <v>97381.47</v>
       </c>
       <c r="D19" t="n">
-        <v>32000</v>
+        <v>32239.71</v>
       </c>
       <c r="E19" t="n">
         <v>113835</v>
       </c>
       <c r="F19" t="n">
-        <v>0.9223876663592041</v>
+        <v>0.8554615891421795</v>
       </c>
       <c r="G19" t="n">
-        <v>147000</v>
+        <v>136334.058</v>
       </c>
       <c r="H19" t="n">
-        <v>1.291342732902886</v>
+        <v>1.197646224799051</v>
+      </c>
+      <c r="J19" t="n">
+        <v>18780.32</v>
+      </c>
+      <c r="L19" t="n">
+        <v>138897.26</v>
       </c>
       <c r="N19" t="n">
-        <v>370000</v>
-      </c>
-      <c r="T19" t="n">
+        <v>356899.68</v>
+      </c>
+      <c r="O19" t="n">
+        <v>145351.38</v>
+      </c>
+      <c r="P19" t="n">
+        <v>2.455426842180652</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>344352.7559055118</v>
+      </c>
+      <c r="R19" t="n">
+        <v>1.036436252881133</v>
+      </c>
+      <c r="S19" t="n">
         <v>874656</v>
       </c>
     </row>
@@ -846,27 +933,45 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>8128.81</v>
+        <v>6718.860000000001</v>
       </c>
       <c r="D20" t="n">
-        <v>18000</v>
+        <v>18412.68</v>
       </c>
       <c r="E20" t="n">
         <v>35000</v>
       </c>
       <c r="F20" t="n">
-        <v>0.2028571428571428</v>
+        <v>0.1919674285714286</v>
       </c>
       <c r="G20" t="n">
-        <v>9940</v>
+        <v>9406.404</v>
       </c>
       <c r="H20" t="n">
-        <v>0.284</v>
+        <v>0.2687544</v>
+      </c>
+      <c r="J20" t="n">
+        <v>9628.32</v>
+      </c>
+      <c r="L20" t="n">
+        <v>3587.36</v>
       </c>
       <c r="N20" t="n">
-        <v>55000</v>
-      </c>
-      <c r="T20" t="n">
+        <v>53336.48</v>
+      </c>
+      <c r="O20" t="n">
+        <v>147744.55</v>
+      </c>
+      <c r="P20" t="n">
+        <v>0.3610047206479021</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>344352.7559055118</v>
+      </c>
+      <c r="R20" t="n">
+        <v>0.1548890754765302</v>
+      </c>
+      <c r="S20" t="n">
         <v>874656</v>
       </c>
     </row>
@@ -877,27 +982,45 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>44635.09</v>
+        <v>39942.76</v>
       </c>
       <c r="D21" t="n">
-        <v>101000</v>
+        <v>101343</v>
       </c>
       <c r="E21" t="n">
         <v>110000</v>
       </c>
       <c r="F21" t="n">
-        <v>0.3818181818181818</v>
+        <v>0.363116</v>
       </c>
       <c r="G21" t="n">
-        <v>58800</v>
+        <v>55919.864</v>
       </c>
       <c r="H21" t="n">
-        <v>0.5345454545454545</v>
+        <v>0.5083624</v>
+      </c>
+      <c r="J21" t="n">
+        <v>42207.69</v>
+      </c>
+      <c r="L21" t="n">
+        <v>17179.69</v>
       </c>
       <c r="N21" t="n">
-        <v>225000</v>
-      </c>
-      <c r="T21" t="n">
+        <v>217468.33</v>
+      </c>
+      <c r="O21" t="n">
+        <v>342609.13</v>
+      </c>
+      <c r="P21" t="n">
+        <v>0.6347417828590849</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>372440.9448818898</v>
+      </c>
+      <c r="R21" t="n">
+        <v>0.5839001672304439</v>
+      </c>
+      <c r="S21" t="n">
         <v>946000</v>
       </c>
     </row>
@@ -908,27 +1031,45 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>44607.56</v>
+        <v>39238.31</v>
       </c>
       <c r="D22" t="n">
-        <v>51000</v>
+        <v>51088.92</v>
       </c>
       <c r="E22" t="n">
         <v>79087</v>
       </c>
       <c r="F22" t="n">
-        <v>0.5184164274785995</v>
+        <v>0.4961410851340928</v>
       </c>
       <c r="G22" t="n">
-        <v>57400</v>
+        <v>54933.634</v>
       </c>
       <c r="H22" t="n">
-        <v>0.7257829984700394</v>
+        <v>0.6945975191877299</v>
+      </c>
+      <c r="J22" t="n">
+        <v>4712.620000000001</v>
+      </c>
+      <c r="L22" t="n">
+        <v>78017.51000000001</v>
       </c>
       <c r="N22" t="n">
-        <v>280000</v>
-      </c>
-      <c r="T22" t="n">
+        <v>272457.47</v>
+      </c>
+      <c r="O22" t="n">
+        <v>418453.72</v>
+      </c>
+      <c r="P22" t="n">
+        <v>0.6511053838880915</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>380133.8582677165</v>
+      </c>
+      <c r="R22" t="n">
+        <v>0.716740863972492</v>
+      </c>
+      <c r="S22" t="n">
         <v>965540</v>
       </c>
     </row>
@@ -939,25 +1080,293 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>837800</v>
+        <v>811129.3699999999</v>
       </c>
       <c r="D23" t="n">
-        <v>1091500</v>
+        <v>1086662.16</v>
       </c>
       <c r="E23" t="n">
         <v>1449422</v>
       </c>
       <c r="F23" t="n">
-        <v>0.5780235155806935</v>
+        <v>0.5596226426810135</v>
       </c>
       <c r="G23" t="n">
-        <v>1172920</v>
+        <v>1135581.118</v>
+      </c>
+      <c r="J23" t="n">
+        <v>537850.6</v>
+      </c>
+      <c r="L23" t="n">
+        <v>1362479.87</v>
       </c>
       <c r="N23" t="n">
-        <v>4863000</v>
-      </c>
-      <c r="T23" t="n">
+        <v>4876991.430000001</v>
+      </c>
+      <c r="O23" t="n">
+        <v>5094670.55</v>
+      </c>
+      <c r="P23" t="n">
+        <v>0.9572731704898957</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>6286949.606299213</v>
+      </c>
+      <c r="R23" t="n">
+        <v>0.7757325468480766</v>
+      </c>
+      <c r="S23" t="n">
         <v>15968852</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>HOUSE/CORP PRODUCTS</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>40.52999999999999</v>
+      </c>
+      <c r="D25" t="n">
+        <v>0</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0</v>
+      </c>
+      <c r="G25" t="n">
+        <v>56.74199999999999</v>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L25" t="n">
+        <v>24014.96</v>
+      </c>
+      <c r="N25" t="n">
+        <v>41227.85</v>
+      </c>
+      <c r="O25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>0</v>
+      </c>
+      <c r="S25" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>ELITE DEALS</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>10236.48</v>
+      </c>
+      <c r="D26" t="n">
+        <v>6512</v>
+      </c>
+      <c r="E26" t="n">
+        <v>5000</v>
+      </c>
+      <c r="F26" t="n">
+        <v>2.047296</v>
+      </c>
+      <c r="G26" t="n">
+        <v>14331.072</v>
+      </c>
+      <c r="H26" t="n">
+        <v>2.8662144</v>
+      </c>
+      <c r="J26" t="n">
+        <v>3106.62</v>
+      </c>
+      <c r="L26" t="n">
+        <v>8133.52</v>
+      </c>
+      <c r="N26" t="n">
+        <v>54725.73</v>
+      </c>
+      <c r="O26" t="n">
+        <v>15460</v>
+      </c>
+      <c r="P26" t="n">
+        <v>3.539827296248383</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>15000</v>
+      </c>
+      <c r="R26" t="n">
+        <v>1.030666666666667</v>
+      </c>
+      <c r="S26" t="n">
+        <v>60000</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>KCB</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>0</v>
+      </c>
+      <c r="D27" t="n">
+        <v>0</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G27" t="n">
+        <v>0</v>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J27" t="n">
+        <v>0</v>
+      </c>
+      <c r="L27" t="n">
+        <v>0</v>
+      </c>
+      <c r="N27" t="n">
+        <v>2084</v>
+      </c>
+      <c r="O27" t="n">
+        <v>48946.48</v>
+      </c>
+      <c r="P27" t="n">
+        <v>0.04257711688358386</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>0</v>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S27" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>NET DIRECT</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>2860.95</v>
+      </c>
+      <c r="D28" t="n">
+        <v>2093</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G28" t="n">
+        <v>4005.33</v>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J28" t="n">
+        <v>0</v>
+      </c>
+      <c r="L28" t="n">
+        <v>0</v>
+      </c>
+      <c r="N28" t="n">
+        <v>20878.29</v>
+      </c>
+      <c r="O28" t="n">
+        <v>2093</v>
+      </c>
+      <c r="P28" t="n">
+        <v>9.975293836598185</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>0</v>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S28" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>WOODLAND DIRECT</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>16911.07</v>
+      </c>
+      <c r="D29" t="n">
+        <v>19025</v>
+      </c>
+      <c r="E29" t="n">
+        <v>25000</v>
+      </c>
+      <c r="F29" t="n">
+        <v>0.6764428000000001</v>
+      </c>
+      <c r="G29" t="n">
+        <v>23675.498</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0.9470199200000001</v>
+      </c>
+      <c r="J29" t="n">
+        <v>10456.56</v>
+      </c>
+      <c r="L29" t="n">
+        <v>8388.15</v>
+      </c>
+      <c r="N29" t="n">
+        <v>80549.52</v>
+      </c>
+      <c r="O29" t="n">
+        <v>93303.85000000001</v>
+      </c>
+      <c r="P29" t="n">
+        <v>0.8633032827691461</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>65000</v>
+      </c>
+      <c r="R29" t="n">
+        <v>1.435443846153846</v>
+      </c>
+      <c r="S29" t="n">
+        <v>265000</v>
       </c>
     </row>
     <row r="30">
@@ -967,34 +1376,46 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>925000</v>
+        <v>841178.3999999998</v>
       </c>
       <c r="D30" t="n">
-        <v>1090000</v>
+        <v>1114292.16</v>
       </c>
       <c r="E30" t="n">
         <v>1479422</v>
       </c>
       <c r="F30" t="n">
-        <v>0.625</v>
+        <v>0.5685858396049267</v>
       </c>
       <c r="G30" t="n">
-        <v>1295000</v>
+        <v>1177649.76</v>
       </c>
       <c r="H30" t="n">
-        <v>0.875</v>
+        <v>0.7960201754468975</v>
+      </c>
+      <c r="J30" t="n">
+        <v>551413.78</v>
       </c>
       <c r="L30" t="n">
-        <v>1380000</v>
+        <v>1403016.5</v>
       </c>
       <c r="N30" t="n">
-        <v>5250000</v>
+        <v>5076456.82</v>
       </c>
       <c r="O30" t="n">
-        <v>5254474</v>
+        <v>5254473.88</v>
+      </c>
+      <c r="P30" t="n">
+        <v>0.966120859278113</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>6366949.606299213</v>
       </c>
       <c r="R30" t="n">
-        <v>15968852</v>
+        <v>0.8252733577161389</v>
+      </c>
+      <c r="S30" t="n">
+        <v>16293852</v>
       </c>
     </row>
     <row r="33">
@@ -1018,9 +1439,95 @@
           <t>REVENUE - YTD</t>
         </is>
       </c>
-      <c r="T33" t="inlineStr">
-        <is>
-          <t>SALES ORDERS - YTD</t>
+    </row>
+    <row r="34">
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Current Year</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Prior Year</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>MTD</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>Budget</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Current Year</t>
+        </is>
+      </c>
+      <c r="Q34" t="inlineStr">
+        <is>
+          <t>Budget</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="C35" s="1" t="n">
+        <v>46173</v>
+      </c>
+      <c r="D35" s="1" t="n">
+        <v>45808</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Quota</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>% Quota</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Forecast</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>% Quota</t>
+        </is>
+      </c>
+      <c r="J35" s="1" t="n">
+        <v>46173</v>
+      </c>
+      <c r="K35" s="1" t="n">
+        <v>46173</v>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>% Budget</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>BALANCE</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>YTD</t>
+        </is>
+      </c>
+      <c r="Q35" t="inlineStr">
+        <is>
+          <t>YTD</t>
+        </is>
+      </c>
+      <c r="R35" t="inlineStr">
+        <is>
+          <t>% Budget</t>
         </is>
       </c>
     </row>
@@ -1031,28 +1538,43 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>580000</v>
+        <v>562070.4299999996</v>
+      </c>
+      <c r="D36" t="n">
+        <v>559409.49</v>
       </c>
       <c r="E36" t="n">
         <v>922307</v>
       </c>
       <c r="F36" t="n">
-        <v>0.628857853187713</v>
+        <v>0.6094179378449904</v>
+      </c>
+      <c r="G36" t="n">
+        <v>786898.6019999994</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0.8531851129829865</v>
       </c>
       <c r="J36" t="n">
-        <v>415000</v>
+        <v>402105.9399999999</v>
       </c>
       <c r="K36" t="n">
-        <v>1034000</v>
+        <v>1034925.60962101</v>
       </c>
       <c r="L36" t="n">
-        <v>0.4013539651837524</v>
+        <v>0.3885360805278083</v>
       </c>
       <c r="N36" t="n">
-        <v>730000</v>
+        <v>714810.0099999997</v>
       </c>
       <c r="P36" t="n">
-        <v>3200000</v>
+        <v>3170930.950000001</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>4217925.872183997</v>
+      </c>
+      <c r="R36" t="n">
+        <v>0.7517749353802955</v>
       </c>
     </row>
     <row r="37">
@@ -1062,28 +1584,43 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>145000</v>
+        <v>138585.47</v>
+      </c>
+      <c r="D37" t="n">
+        <v>371134.49</v>
       </c>
       <c r="E37" t="n">
         <v>345615</v>
       </c>
       <c r="F37" t="n">
-        <v>0.4195419758980368</v>
+        <v>0.4009822201004007</v>
+      </c>
+      <c r="G37" t="n">
+        <v>194019.658</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0.5613751081405611</v>
       </c>
       <c r="J37" t="n">
-        <v>95000</v>
+        <v>90353.84000000001</v>
       </c>
       <c r="K37" t="n">
-        <v>346000</v>
+        <v>346129.0353576827</v>
       </c>
       <c r="L37" t="n">
-        <v>0.2745664739884393</v>
+        <v>0.26104091471734</v>
       </c>
       <c r="N37" t="n">
-        <v>520000</v>
+        <v>515457.22</v>
       </c>
       <c r="P37" t="n">
-        <v>720000</v>
+        <v>710696.0099999999</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>1455339.438949773</v>
+      </c>
+      <c r="R37" t="n">
+        <v>0.4883369411831955</v>
       </c>
     </row>
     <row r="38">
@@ -1093,19 +1630,28 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>58000</v>
+        <v>56385</v>
+      </c>
+      <c r="D38" t="n">
+        <v>71782</v>
       </c>
       <c r="E38" t="n">
         <v>54500</v>
       </c>
       <c r="F38" t="n">
-        <v>1.064220183486239</v>
+        <v>1.034587155963303</v>
+      </c>
+      <c r="G38" t="n">
+        <v>78939</v>
+      </c>
+      <c r="H38" t="n">
+        <v>1.448422018348624</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
       </c>
       <c r="K38" t="n">
-        <v>25000</v>
+        <v>24960.78912</v>
       </c>
       <c r="L38" t="n">
         <v>0</v>
@@ -1114,7 +1660,13 @@
         <v>0</v>
       </c>
       <c r="P38" t="n">
-        <v>32000</v>
+        <v>32032.38</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>102624.81632</v>
+      </c>
+      <c r="R38" t="n">
+        <v>0.3121309362456552</v>
       </c>
     </row>
     <row r="39">
@@ -1126,26 +1678,41 @@
       <c r="C39" t="n">
         <v>0</v>
       </c>
+      <c r="D39" t="n">
+        <v>36388.18</v>
+      </c>
       <c r="E39" t="n">
         <v>57000</v>
       </c>
       <c r="F39" t="n">
         <v>0</v>
       </c>
+      <c r="G39" t="n">
+        <v>0</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0</v>
+      </c>
       <c r="J39" t="n">
-        <v>11000</v>
+        <v>10715</v>
       </c>
       <c r="K39" t="n">
-        <v>28000</v>
+        <v>27961.42744319999</v>
       </c>
       <c r="L39" t="n">
-        <v>0.3928571428571428</v>
+        <v>0.3832064733378198</v>
       </c>
       <c r="N39" t="n">
         <v>0</v>
       </c>
       <c r="P39" t="n">
-        <v>112000</v>
+        <v>109836.85</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>106173.1688352</v>
+      </c>
+      <c r="R39" t="n">
+        <v>1.034506657425726</v>
       </c>
     </row>
     <row r="40">
@@ -1155,28 +1722,43 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>87000</v>
+        <v>84137.5</v>
+      </c>
+      <c r="D40" t="n">
+        <v>75578</v>
       </c>
       <c r="E40" t="n">
         <v>100000</v>
       </c>
       <c r="F40" t="n">
-        <v>0.87</v>
+        <v>0.841375</v>
+      </c>
+      <c r="G40" t="n">
+        <v>117792.5</v>
+      </c>
+      <c r="H40" t="n">
+        <v>1.177925</v>
       </c>
       <c r="J40" t="n">
-        <v>50000</v>
+        <v>48239</v>
       </c>
       <c r="K40" t="n">
-        <v>100000</v>
+        <v>99999.12329999999</v>
       </c>
       <c r="L40" t="n">
-        <v>0.5</v>
+        <v>0.482394229150207</v>
       </c>
       <c r="N40" t="n">
-        <v>162000</v>
+        <v>159341.5</v>
       </c>
       <c r="P40" t="n">
-        <v>248000</v>
+        <v>243378</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>490258.9863</v>
+      </c>
+      <c r="R40" t="n">
+        <v>0.4964274124514911</v>
       </c>
     </row>
     <row r="41">
@@ -1188,6 +1770,9 @@
       <c r="C41" t="n">
         <v>0</v>
       </c>
+      <c r="D41" t="n">
+        <v>0</v>
+      </c>
       <c r="E41" t="n">
         <v>0</v>
       </c>
@@ -1196,6 +1781,9 @@
           <t>-</t>
         </is>
       </c>
+      <c r="G41" t="n">
+        <v>0</v>
+      </c>
       <c r="J41" t="n">
         <v>0</v>
       </c>
@@ -1208,10 +1796,18 @@
         </is>
       </c>
       <c r="N41" t="n">
-        <v>17000</v>
+        <v>16544.12</v>
       </c>
       <c r="P41" t="n">
         <v>0</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>0</v>
+      </c>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="42">
@@ -1223,6 +1819,9 @@
       <c r="C42" t="n">
         <v>0</v>
       </c>
+      <c r="D42" t="n">
+        <v>0</v>
+      </c>
       <c r="E42" t="n">
         <v>0</v>
       </c>
@@ -1231,6 +1830,9 @@
           <t>-</t>
         </is>
       </c>
+      <c r="G42" t="n">
+        <v>0</v>
+      </c>
       <c r="J42" t="n">
         <v>0</v>
       </c>
@@ -1247,6 +1849,14 @@
       </c>
       <c r="P42" t="n">
         <v>0</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>0</v>
+      </c>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="43">
@@ -1256,25 +1866,43 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>870000</v>
+        <v>841178.3999999996</v>
+      </c>
+      <c r="D43" t="n">
+        <v>1114292.16</v>
       </c>
       <c r="E43" t="n">
         <v>1479422</v>
       </c>
+      <c r="F43" t="n">
+        <v>0.5685858396049265</v>
+      </c>
+      <c r="G43" t="n">
+        <v>1177649.759999999</v>
+      </c>
+      <c r="H43" t="n">
+        <v>0.7960201754468971</v>
+      </c>
       <c r="J43" t="n">
-        <v>571000</v>
+        <v>551413.78</v>
       </c>
       <c r="K43" t="n">
-        <v>1533000</v>
+        <v>1533975.984841893</v>
       </c>
       <c r="L43" t="n">
-        <v>0.3724722765818656</v>
+        <v>0.3594670225928173</v>
       </c>
       <c r="N43" t="n">
-        <v>1429000</v>
+        <v>1406152.85</v>
       </c>
       <c r="P43" t="n">
-        <v>4312000</v>
+        <v>4266874.190000001</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>6372322.282588971</v>
+      </c>
+      <c r="R43" t="n">
+        <v>0.6695948511044925</v>
       </c>
     </row>
     <row r="44">
@@ -1283,11 +1911,38 @@
           <t>FREIGHT</t>
         </is>
       </c>
+      <c r="C44" t="n">
+        <v>0</v>
+      </c>
+      <c r="D44" t="n">
+        <v>0</v>
+      </c>
+      <c r="E44" t="n">
+        <v>0</v>
+      </c>
+      <c r="G44" t="n">
+        <v>0</v>
+      </c>
       <c r="J44" t="n">
-        <v>46000</v>
+        <v>44536.09</v>
+      </c>
+      <c r="K44" t="n">
+        <v>83161.76075410369</v>
+      </c>
+      <c r="L44" t="n">
+        <v>0.5355356788522821</v>
+      </c>
+      <c r="N44" t="n">
+        <v>0</v>
       </c>
       <c r="P44" t="n">
-        <v>278000</v>
+        <v>272054.11</v>
+      </c>
+      <c r="Q44" t="n">
+        <v>341625.6024159174</v>
+      </c>
+      <c r="R44" t="n">
+        <v>0.7963516436592578</v>
       </c>
     </row>
     <row r="45">
@@ -1296,233 +1951,48 @@
           <t>TOTAL W/ FREIGHT</t>
         </is>
       </c>
+      <c r="C45" t="n">
+        <v>841178.3999999996</v>
+      </c>
+      <c r="D45" t="n">
+        <v>1114292.16</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G45" t="n">
+        <v>1177649.759999999</v>
+      </c>
       <c r="J45" t="n">
-        <v>680000</v>
+        <v>595949.87</v>
       </c>
       <c r="K45" t="n">
-        <v>1617138</v>
+        <v>1617137.745595997</v>
       </c>
       <c r="L45" t="n">
-        <v>0.42</v>
+        <v>0.3685214024735798</v>
+      </c>
+      <c r="N45" t="n">
+        <v>1406152.85</v>
       </c>
       <c r="P45" t="n">
-        <v>4750000</v>
+        <v>4538928.300000002</v>
       </c>
       <c r="Q45" t="n">
-        <v>6713948</v>
+        <v>6713947.885004888</v>
       </c>
       <c r="R45" t="n">
-        <v>0.708</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:A1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>[PROXY DATA - BY CUSTOMER]</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:A1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>[PROXY DATA - BACKLOG_info]</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:A1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>[PROXY DATA - BY GROUP]</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:A1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>[PROXY DATA - BY ITEM-FP]</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:A1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>[PROXY DATA - REVENUE-DIRECT]</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:A1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>[PROXY DATA - REVENUE_INPUT]</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:A1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>[PROXY DATA - BY ITEM-PAV]</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:A1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>[PROXY DATA - BY TYPE]</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:A1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>[PROXY DATA - SALESPERSON]</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:A1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>[PROXY DATA - BY DISTRIBUTOR]</t>
-        </is>
+        <v>0.6760446130565544</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="G46" t="n">
+        <v>0</v>
+      </c>
+      <c r="N46" t="n">
+        <v>3136.350000000093</v>
       </c>
     </row>
   </sheetData>
@@ -1536,7 +2006,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G18"/>
+  <dimension ref="A1:G19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1551,822 +2021,404 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Sum of REVENUE</t>
-        </is>
-      </c>
-    </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>SALES REP</t>
+          <t>Sum of REVENUE</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Jan</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Feb</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Mar</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Apr</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>May</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Grand Total</t>
+          <t>Months (Date)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ELITE DEALS</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>21000</v>
-      </c>
-      <c r="C4" t="n">
-        <v>8100</v>
-      </c>
-      <c r="D4" t="n">
-        <v>4600</v>
-      </c>
-      <c r="E4" t="n">
-        <v>11200</v>
-      </c>
-      <c r="F4" t="n">
-        <v>3200</v>
-      </c>
-      <c r="G4" t="n">
-        <v>48100</v>
+          <t>SALES REP</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Jan</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Feb</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Mar</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Apr</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>May</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Grand Total</t>
+        </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ERIC BLASKOWSKI</t>
+          <t>ELITE DEALS</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>173000</v>
+        <v>20883.4</v>
       </c>
       <c r="C5" t="n">
-        <v>137000</v>
+        <v>8092.18</v>
       </c>
       <c r="D5" t="n">
-        <v>166000</v>
+        <v>4557.53</v>
       </c>
       <c r="E5" t="n">
-        <v>274000</v>
+        <v>11196.48</v>
       </c>
       <c r="F5" t="n">
-        <v>136000</v>
+        <v>3106.62</v>
       </c>
       <c r="G5" t="n">
-        <v>886000</v>
+        <v>47836.21000000001</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>KCB</t>
+          <t>ERIC BLASKOWSKI</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0</v>
+        <v>172905.2999999999</v>
       </c>
       <c r="C6" t="n">
-        <v>2084</v>
+        <v>137414.86</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>165774.44</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>273320.11</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>135546.3</v>
       </c>
       <c r="G6" t="n">
-        <v>2084</v>
+        <v>884961.01</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>KEVIN KEITH</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>185000</v>
+          <t>KCB</t>
+        </is>
       </c>
       <c r="C7" t="n">
-        <v>152000</v>
-      </c>
-      <c r="D7" t="n">
-        <v>193000</v>
-      </c>
-      <c r="E7" t="n">
-        <v>312000</v>
-      </c>
-      <c r="F7" t="n">
-        <v>87000</v>
+        <v>2084</v>
       </c>
       <c r="G7" t="n">
-        <v>929000</v>
+        <v>2084</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>NET DIRECT</t>
+          <t>KEVIN KEITH</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0</v>
+        <v>184892.87</v>
       </c>
       <c r="C8" t="n">
-        <v>0</v>
+        <v>151654.09</v>
       </c>
       <c r="D8" t="n">
-        <v>18000</v>
+        <v>192332.91</v>
       </c>
       <c r="E8" t="n">
-        <v>0</v>
+        <v>311281.82</v>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>86191.32999999996</v>
       </c>
       <c r="G8" t="n">
-        <v>18000</v>
+        <v>926353.0199999999</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>THORNTON COLE</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>292000</v>
-      </c>
-      <c r="C9" t="n">
-        <v>178000</v>
+          <t>NET DIRECT</t>
+        </is>
       </c>
       <c r="D9" t="n">
-        <v>343000</v>
-      </c>
-      <c r="E9" t="n">
-        <v>321000</v>
-      </c>
-      <c r="F9" t="n">
-        <v>222000</v>
+        <v>18017.34</v>
       </c>
       <c r="G9" t="n">
-        <v>1356000</v>
+        <v>18017.34</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>WOODLAND DIRECT</t>
+          <t>THORNTON COLE</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>25000</v>
+        <v>291224.3699999999</v>
       </c>
       <c r="C10" t="n">
-        <v>7600</v>
+        <v>177306.69</v>
       </c>
       <c r="D10" t="n">
-        <v>18600</v>
+        <v>342650.01</v>
       </c>
       <c r="E10" t="n">
-        <v>13100</v>
+        <v>320793.4400000001</v>
       </c>
       <c r="F10" t="n">
-        <v>10500</v>
+        <v>220975.64</v>
       </c>
       <c r="G10" t="n">
-        <v>74800</v>
+        <v>1352950.15</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>HOUSE</t>
+          <t>WOODLAND DIRECT</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0</v>
+        <v>25027.94</v>
       </c>
       <c r="C11" t="n">
-        <v>0</v>
+        <v>7557.52</v>
       </c>
       <c r="D11" t="n">
-        <v>0</v>
+        <v>18627.35</v>
       </c>
       <c r="E11" t="n">
-        <v>0</v>
+        <v>13076</v>
       </c>
       <c r="F11" t="n">
-        <v>0</v>
+        <v>10456.56</v>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>74745.37</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>TIFFANY HASEKER</t>
+          <t>HOUSE</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>45000</v>
+        <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>5300</v>
+        <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>89000</v>
+        <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>90000</v>
+        <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>4800</v>
+        <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>234100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>SUZANNE HORST</t>
+          <t>TIFFANY HASEKER</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>67000</v>
+        <v>44660.09</v>
       </c>
       <c r="C13" t="n">
-        <v>30700</v>
+        <v>5262.04</v>
       </c>
       <c r="D13" t="n">
-        <v>69500</v>
+        <v>88811.11</v>
       </c>
       <c r="E13" t="n">
-        <v>32300</v>
+        <v>89737.33</v>
       </c>
       <c r="F13" t="n">
-        <v>42500</v>
+        <v>4712.620000000001</v>
       </c>
       <c r="G13" t="n">
-        <v>242000</v>
+        <v>233183.19</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>MICHAEL KUHLMAN</t>
+          <t>SUZANNE HORST</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>15200</v>
+        <v>66794.44</v>
       </c>
       <c r="C14" t="n">
-        <v>23700</v>
+        <v>30664.01</v>
       </c>
       <c r="D14" t="n">
-        <v>7300</v>
+        <v>69322.32999999999</v>
       </c>
       <c r="E14" t="n">
-        <v>0</v>
+        <v>32238.09</v>
       </c>
       <c r="F14" t="n">
-        <v>11500</v>
+        <v>42207.69</v>
       </c>
       <c r="G14" t="n">
-        <v>57700</v>
+        <v>241226.56</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>GRAY MOOREHEAD</t>
+          <t>MICHAEL KUHLMAN</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>31000</v>
+        <v>15212.41</v>
       </c>
       <c r="C15" t="n">
-        <v>38000</v>
+        <v>23667.3</v>
       </c>
       <c r="D15" t="n">
-        <v>47000</v>
+        <v>7292.070000000001</v>
       </c>
       <c r="E15" t="n">
-        <v>125500</v>
+        <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>19000</v>
+        <v>11430.6</v>
       </c>
       <c r="G15" t="n">
-        <v>260500</v>
+        <v>57602.38</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>HAMP BRILEY</t>
+          <t>GRAY MOOREHEAD</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1100</v>
+        <v>30605.95</v>
       </c>
       <c r="C16" t="n">
-        <v>17700</v>
+        <v>37989.4</v>
       </c>
       <c r="D16" t="n">
-        <v>28600</v>
+        <v>46745.63000000001</v>
       </c>
       <c r="E16" t="n">
-        <v>57100</v>
+        <v>125489.73</v>
       </c>
       <c r="F16" t="n">
-        <v>8400</v>
+        <v>18780.32</v>
       </c>
       <c r="G16" t="n">
-        <v>112900</v>
+        <v>259611.03</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>BEAU BOUTHILLIER</t>
+          <t>HAMP BRILEY</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>8500</v>
+        <v>1081</v>
       </c>
       <c r="C17" t="n">
-        <v>2300</v>
+        <v>17671.98</v>
       </c>
       <c r="D17" t="n">
-        <v>5100</v>
+        <v>28605.25999999999</v>
       </c>
       <c r="E17" t="n">
-        <v>30100</v>
+        <v>57049.81999999999</v>
       </c>
       <c r="F17" t="n">
-        <v>9700</v>
+        <v>8377.780000000001</v>
       </c>
       <c r="G17" t="n">
-        <v>55700</v>
+        <v>112785.84</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
+          <t>BEAU BOUTHILLIER</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>8403.85</v>
+      </c>
+      <c r="C18" t="n">
+        <v>2311.2</v>
+      </c>
+      <c r="D18" t="n">
+        <v>5087.52</v>
+      </c>
+      <c r="E18" t="n">
+        <v>30087.2</v>
+      </c>
+      <c r="F18" t="n">
+        <v>9628.32</v>
+      </c>
+      <c r="G18" t="n">
+        <v>55518.09</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
           <t>Grand Total</t>
         </is>
       </c>
-      <c r="B18" t="n">
-        <v>863800</v>
-      </c>
-      <c r="C18" t="n">
-        <v>602484</v>
-      </c>
-      <c r="D18" t="n">
-        <v>989700</v>
-      </c>
-      <c r="E18" t="n">
-        <v>1266300</v>
-      </c>
-      <c r="F18" t="n">
-        <v>554600</v>
-      </c>
-      <c r="G18" t="n">
-        <v>4276884</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:A1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>[PROXY DATA - FIREPLACE]</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:A1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>[PROXY DATA - PAVERS]</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:A1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>[PROXY DATA - SWD]</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:A1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>[PROXY DATA - OTHER]</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:A1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>[PROXY DATA - FLOORING]</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:A1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>[PROXY DATA - INSTALL]</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:A1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>[PROXY DATA - DETAIL_ALL]</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:A1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>[PROXY DATA - FIREPLACE (2)]</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:A1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>[PROXY DATA - BACKLOG_INPUT]</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:A1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>[PROXY DATA - CUSTOMER]</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:A1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>[PROXY DATA - FORECAST]</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:A1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>[PROXY DATA - NOTE]</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:A1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>[PROXY DATA - ITEM]</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:A1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>[PROXY DATA - PRODUCT2]</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:A1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>[PROXY DATA - DAILYORDERS]</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:A1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>[PROXY DATA - BACKLOG]</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:A1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>[PROXY DATA - BYREPBYSTATE]</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:A1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>[PROXY DATA - BY PRODUCT]</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:A1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>[PROXY DATA - MTDbyORDER]</t>
-        </is>
+      <c r="B19" t="n">
+        <v>861691.6199999999</v>
+      </c>
+      <c r="C19" t="n">
+        <v>601675.27</v>
+      </c>
+      <c r="D19" t="n">
+        <v>987823.5</v>
+      </c>
+      <c r="E19" t="n">
+        <v>1264270.02</v>
+      </c>
+      <c r="F19" t="n">
+        <v>551413.7799999998</v>
+      </c>
+      <c r="G19" t="n">
+        <v>4266874.189999999</v>
       </c>
     </row>
   </sheetData>

--- a/sales_report.xlsx
+++ b/sales_report.xlsx
@@ -435,8 +435,10 @@
       </c>
     </row>
     <row r="3">
-      <c r="B3" s="1" t="n">
-        <v>46163</v>
+      <c r="B3" s="1" t="inlineStr">
+        <is>
+          <t>TEST RUN 2099</t>
+        </is>
       </c>
     </row>
     <row r="4">
@@ -456,7 +458,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -464,7 +466,7 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>254</v>
+        <v>250</v>
       </c>
     </row>
     <row r="6">
@@ -474,10 +476,10 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E6" t="n">
-        <v>0.7142857142857143</v>
+        <v>0.5</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -485,10 +487,10 @@
         </is>
       </c>
       <c r="K6" t="n">
-        <v>100</v>
+        <v>125</v>
       </c>
       <c r="L6" t="n">
-        <v>0.3937007874015748</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="7">
@@ -1376,34 +1378,34 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>841178.3999999998</v>
+        <v>2000000</v>
       </c>
       <c r="D30" t="n">
-        <v>1114292.16</v>
+        <v>1000000</v>
       </c>
       <c r="E30" t="n">
-        <v>1479422</v>
+        <v>2500000</v>
       </c>
       <c r="F30" t="n">
-        <v>0.5685858396049267</v>
+        <v>0.8</v>
       </c>
       <c r="G30" t="n">
-        <v>1177649.76</v>
+        <v>3000000</v>
       </c>
       <c r="H30" t="n">
-        <v>0.7960201754468975</v>
+        <v>1.2</v>
       </c>
       <c r="J30" t="n">
         <v>551413.78</v>
       </c>
       <c r="L30" t="n">
-        <v>1403016.5</v>
+        <v>9000000</v>
       </c>
       <c r="N30" t="n">
-        <v>5076456.82</v>
+        <v>7000000</v>
       </c>
       <c r="O30" t="n">
-        <v>5254473.88</v>
+        <v>6000000</v>
       </c>
       <c r="P30" t="n">
         <v>0.966120859278113</v>
@@ -1415,7 +1417,7 @@
         <v>0.8252733577161389</v>
       </c>
       <c r="S30" t="n">
-        <v>16293852</v>
+        <v>20000000</v>
       </c>
     </row>
     <row r="33">
@@ -1966,25 +1968,25 @@
         <v>1177649.759999999</v>
       </c>
       <c r="J45" t="n">
-        <v>595949.87</v>
+        <v>1500000</v>
       </c>
       <c r="K45" t="n">
-        <v>1617137.745595997</v>
+        <v>2000000</v>
       </c>
       <c r="L45" t="n">
-        <v>0.3685214024735798</v>
+        <v>0.75</v>
       </c>
       <c r="N45" t="n">
         <v>1406152.85</v>
       </c>
       <c r="P45" t="n">
-        <v>4538928.300000002</v>
+        <v>8000000</v>
       </c>
       <c r="Q45" t="n">
-        <v>6713947.885004888</v>
+        <v>10000000</v>
       </c>
       <c r="R45" t="n">
-        <v>0.6760446130565544</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="46">

--- a/sales_report.xlsx
+++ b/sales_report.xlsx
@@ -641,22 +641,22 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>203881.14</v>
+        <v>500000</v>
       </c>
       <c r="D14" t="n">
-        <v>267482.78</v>
+        <v>300000</v>
       </c>
       <c r="E14" t="n">
-        <v>352500</v>
+        <v>600000</v>
       </c>
       <c r="F14" t="n">
-        <v>0.5783862127659575</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="G14" t="n">
-        <v>285433.596</v>
+        <v>750000</v>
       </c>
       <c r="H14" t="n">
-        <v>0.8097406978723405</v>
+        <v>1.25</v>
       </c>
       <c r="J14" t="n">
         <v>135546.3</v>
@@ -665,10 +665,10 @@
         <v>453038.5399999997</v>
       </c>
       <c r="N14" t="n">
-        <v>1119347.93</v>
+        <v>2500000</v>
       </c>
       <c r="O14" t="n">
-        <v>1027472.71</v>
+        <v>2125000</v>
       </c>
       <c r="P14" t="n">
         <v>1.089418647430548</v>
@@ -680,7 +680,7 @@
         <v>0.8123267834857143</v>
       </c>
       <c r="S14" t="n">
-        <v>3500000</v>
+        <v>6000000</v>
       </c>
     </row>
     <row r="15">
@@ -690,22 +690,22 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>173446.83</v>
+        <v>450000</v>
       </c>
       <c r="D15" t="n">
-        <v>232668.87</v>
+        <v>270000</v>
       </c>
       <c r="E15" t="n">
-        <v>253000</v>
+        <v>500000</v>
       </c>
       <c r="F15" t="n">
-        <v>0.6855605928853755</v>
+        <v>0.9</v>
       </c>
       <c r="G15" t="n">
-        <v>242825.562</v>
+        <v>675000</v>
       </c>
       <c r="H15" t="n">
-        <v>0.9597848300395259</v>
+        <v>1.35</v>
       </c>
       <c r="J15" t="n">
         <v>86191.32999999996</v>
@@ -714,10 +714,10 @@
         <v>343414.89</v>
       </c>
       <c r="N15" t="n">
-        <v>1126113.49</v>
+        <v>2200000</v>
       </c>
       <c r="O15" t="n">
-        <v>1012533.76</v>
+        <v>1870000</v>
       </c>
       <c r="P15" t="n">
         <v>1.112173770877526</v>
@@ -729,7 +729,7 @@
         <v>1.114703142868277</v>
       </c>
       <c r="S15" t="n">
-        <v>2566000</v>
+        <v>5000000</v>
       </c>
     </row>
     <row r="16">
@@ -739,22 +739,22 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>234020.21</v>
+        <v>600000</v>
       </c>
       <c r="D16" t="n">
-        <v>365540.12</v>
+        <v>360000</v>
       </c>
       <c r="E16" t="n">
-        <v>406000</v>
+        <v>650000</v>
       </c>
       <c r="F16" t="n">
-        <v>0.5764044581280788</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="G16" t="n">
-        <v>327628.2940000001</v>
+        <v>900000</v>
       </c>
       <c r="H16" t="n">
-        <v>0.8069662413793105</v>
+        <v>1.384615384615385</v>
       </c>
       <c r="J16" t="n">
         <v>220975.64</v>
@@ -763,10 +763,10 @@
         <v>291565.36</v>
       </c>
       <c r="N16" t="n">
-        <v>1533379.040000001</v>
+        <v>3000000</v>
       </c>
       <c r="O16" t="n">
-        <v>1772306.06</v>
+        <v>2550000</v>
       </c>
       <c r="P16" t="n">
         <v>0.8651886232336194</v>
@@ -778,7 +778,7 @@
         <v>0.8612964974789918</v>
       </c>
       <c r="S16" t="n">
-        <v>4522000</v>
+        <v>7000000</v>
       </c>
     </row>
     <row r="17">
@@ -788,22 +788,22 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>7664.599999999999</v>
+        <v>300000</v>
       </c>
       <c r="D17" t="n">
-        <v>10260.86</v>
+        <v>180000</v>
       </c>
       <c r="E17" t="n">
-        <v>35000</v>
+        <v>400000</v>
       </c>
       <c r="F17" t="n">
-        <v>0.2189885714285714</v>
+        <v>0.75</v>
       </c>
       <c r="G17" t="n">
-        <v>10730.44</v>
+        <v>450000</v>
       </c>
       <c r="H17" t="n">
-        <v>0.306584</v>
+        <v>1.125</v>
       </c>
       <c r="J17" t="n">
         <v>11430.6</v>
@@ -812,10 +812,10 @@
         <v>16544.12</v>
       </c>
       <c r="N17" t="n">
-        <v>51293.38</v>
+        <v>1500000</v>
       </c>
       <c r="O17" t="n">
-        <v>68651.59</v>
+        <v>1275000</v>
       </c>
       <c r="P17" t="n">
         <v>0.7471550185509177</v>
@@ -827,7 +827,7 @@
         <v>0.1163260582142857</v>
       </c>
       <c r="S17" t="n">
-        <v>1120000</v>
+        <v>4000000</v>
       </c>
     </row>
     <row r="18">
@@ -837,22 +837,22 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>8835.190000000001</v>
+        <v>250000</v>
       </c>
       <c r="D18" t="n">
-        <v>7625.219999999999</v>
+        <v>150000</v>
       </c>
       <c r="E18" t="n">
-        <v>65000</v>
+        <v>350000</v>
       </c>
       <c r="F18" t="n">
-        <v>0.135926</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="G18" t="n">
-        <v>12369.266</v>
+        <v>375000</v>
       </c>
       <c r="H18" t="n">
-        <v>0.1902964</v>
+        <v>1.071428571428571</v>
       </c>
       <c r="J18" t="n">
         <v>8377.780000000001</v>
@@ -861,10 +861,10 @@
         <v>20235.14</v>
       </c>
       <c r="N18" t="n">
-        <v>146695.63</v>
+        <v>1200000</v>
       </c>
       <c r="O18" t="n">
-        <v>159547.65</v>
+        <v>1020000</v>
       </c>
       <c r="P18" t="n">
         <v>0.919447136952503</v>
@@ -876,7 +876,7 @@
         <v>0.6210115003333333</v>
       </c>
       <c r="S18" t="n">
-        <v>600000</v>
+        <v>3500000</v>
       </c>
     </row>
     <row r="19">
@@ -886,22 +886,22 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>97381.47</v>
+        <v>550000</v>
       </c>
       <c r="D19" t="n">
-        <v>32239.71</v>
+        <v>330000</v>
       </c>
       <c r="E19" t="n">
-        <v>113835</v>
+        <v>580000</v>
       </c>
       <c r="F19" t="n">
-        <v>0.8554615891421795</v>
+        <v>0.9482758620689655</v>
       </c>
       <c r="G19" t="n">
-        <v>136334.058</v>
+        <v>825000</v>
       </c>
       <c r="H19" t="n">
-        <v>1.197646224799051</v>
+        <v>1.422413793103448</v>
       </c>
       <c r="J19" t="n">
         <v>18780.32</v>
@@ -910,10 +910,10 @@
         <v>138897.26</v>
       </c>
       <c r="N19" t="n">
-        <v>356899.68</v>
+        <v>2700000</v>
       </c>
       <c r="O19" t="n">
-        <v>145351.38</v>
+        <v>2295000</v>
       </c>
       <c r="P19" t="n">
         <v>2.455426842180652</v>
@@ -925,7 +925,7 @@
         <v>1.036436252881133</v>
       </c>
       <c r="S19" t="n">
-        <v>874656</v>
+        <v>5800000</v>
       </c>
     </row>
     <row r="20">
@@ -935,22 +935,22 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>6718.860000000001</v>
+        <v>200000</v>
       </c>
       <c r="D20" t="n">
-        <v>18412.68</v>
+        <v>120000</v>
       </c>
       <c r="E20" t="n">
-        <v>35000</v>
+        <v>300000</v>
       </c>
       <c r="F20" t="n">
-        <v>0.1919674285714286</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="G20" t="n">
-        <v>9406.404</v>
+        <v>300000</v>
       </c>
       <c r="H20" t="n">
-        <v>0.2687544</v>
+        <v>1</v>
       </c>
       <c r="J20" t="n">
         <v>9628.32</v>
@@ -959,10 +959,10 @@
         <v>3587.36</v>
       </c>
       <c r="N20" t="n">
-        <v>53336.48</v>
+        <v>1000000</v>
       </c>
       <c r="O20" t="n">
-        <v>147744.55</v>
+        <v>850000</v>
       </c>
       <c r="P20" t="n">
         <v>0.3610047206479021</v>
@@ -974,7 +974,7 @@
         <v>0.1548890754765302</v>
       </c>
       <c r="S20" t="n">
-        <v>874656</v>
+        <v>3000000</v>
       </c>
     </row>
     <row r="21">
@@ -984,22 +984,22 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>39942.76</v>
+        <v>400000</v>
       </c>
       <c r="D21" t="n">
-        <v>101343</v>
+        <v>240000</v>
       </c>
       <c r="E21" t="n">
-        <v>110000</v>
+        <v>450000</v>
       </c>
       <c r="F21" t="n">
-        <v>0.363116</v>
+        <v>0.8888888888888888</v>
       </c>
       <c r="G21" t="n">
-        <v>55919.864</v>
+        <v>600000</v>
       </c>
       <c r="H21" t="n">
-        <v>0.5083624</v>
+        <v>1.333333333333333</v>
       </c>
       <c r="J21" t="n">
         <v>42207.69</v>
@@ -1008,10 +1008,10 @@
         <v>17179.69</v>
       </c>
       <c r="N21" t="n">
-        <v>217468.33</v>
+        <v>1900000</v>
       </c>
       <c r="O21" t="n">
-        <v>342609.13</v>
+        <v>1615000</v>
       </c>
       <c r="P21" t="n">
         <v>0.6347417828590849</v>
@@ -1023,7 +1023,7 @@
         <v>0.5839001672304439</v>
       </c>
       <c r="S21" t="n">
-        <v>946000</v>
+        <v>4500000</v>
       </c>
     </row>
     <row r="22">
@@ -1033,22 +1033,22 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>39238.31</v>
+        <v>350000</v>
       </c>
       <c r="D22" t="n">
-        <v>51088.92</v>
+        <v>210000</v>
       </c>
       <c r="E22" t="n">
-        <v>79087</v>
+        <v>420000</v>
       </c>
       <c r="F22" t="n">
-        <v>0.4961410851340928</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="G22" t="n">
-        <v>54933.634</v>
+        <v>525000</v>
       </c>
       <c r="H22" t="n">
-        <v>0.6945975191877299</v>
+        <v>1.25</v>
       </c>
       <c r="J22" t="n">
         <v>4712.620000000001</v>
@@ -1057,10 +1057,10 @@
         <v>78017.51000000001</v>
       </c>
       <c r="N22" t="n">
-        <v>272457.47</v>
+        <v>1700000</v>
       </c>
       <c r="O22" t="n">
-        <v>418453.72</v>
+        <v>1445000</v>
       </c>
       <c r="P22" t="n">
         <v>0.6511053838880915</v>
@@ -1072,7 +1072,7 @@
         <v>0.716740863972492</v>
       </c>
       <c r="S22" t="n">
-        <v>965540</v>
+        <v>4200000</v>
       </c>
     </row>
     <row r="23">
@@ -1082,19 +1082,22 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>811129.3699999999</v>
+        <v>3600000</v>
       </c>
       <c r="D23" t="n">
-        <v>1086662.16</v>
+        <v>2160000</v>
       </c>
       <c r="E23" t="n">
-        <v>1449422</v>
+        <v>4250000</v>
       </c>
       <c r="F23" t="n">
-        <v>0.5596226426810135</v>
+        <v>0.8470588235294118</v>
       </c>
       <c r="G23" t="n">
-        <v>1135581.118</v>
+        <v>5400000</v>
+      </c>
+      <c r="H23" t="n">
+        <v>1.270588235294118</v>
       </c>
       <c r="J23" t="n">
         <v>537850.6</v>
@@ -1103,10 +1106,10 @@
         <v>1362479.87</v>
       </c>
       <c r="N23" t="n">
-        <v>4876991.430000001</v>
+        <v>17700000</v>
       </c>
       <c r="O23" t="n">
-        <v>5094670.55</v>
+        <v>15045000</v>
       </c>
       <c r="P23" t="n">
         <v>0.9572731704898957</v>
@@ -1118,7 +1121,7 @@
         <v>0.7757325468480766</v>
       </c>
       <c r="S23" t="n">
-        <v>15968852</v>
+        <v>43000000</v>
       </c>
     </row>
     <row r="25">
@@ -1378,22 +1381,22 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>2000000</v>
+        <v>3600000</v>
       </c>
       <c r="D30" t="n">
-        <v>1000000</v>
+        <v>2160000</v>
       </c>
       <c r="E30" t="n">
-        <v>2500000</v>
+        <v>4250000</v>
       </c>
       <c r="F30" t="n">
-        <v>0.8</v>
+        <v>0.8470588235294118</v>
       </c>
       <c r="G30" t="n">
-        <v>3000000</v>
+        <v>5400000</v>
       </c>
       <c r="H30" t="n">
-        <v>1.2</v>
+        <v>1.270588235294118</v>
       </c>
       <c r="J30" t="n">
         <v>551413.78</v>
@@ -1402,10 +1405,10 @@
         <v>9000000</v>
       </c>
       <c r="N30" t="n">
-        <v>7000000</v>
+        <v>17700000</v>
       </c>
       <c r="O30" t="n">
-        <v>6000000</v>
+        <v>15045000</v>
       </c>
       <c r="P30" t="n">
         <v>0.966120859278113</v>
@@ -1417,7 +1420,7 @@
         <v>0.8252733577161389</v>
       </c>
       <c r="S30" t="n">
-        <v>20000000</v>
+        <v>43000000</v>
       </c>
     </row>
     <row r="33">

--- a/sales_report.xlsx
+++ b/sales_report.xlsx
@@ -742,7 +742,7 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B3" s="3" t="n">
-        <v>46174</v>
+        <v>46175</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -772,21 +772,21 @@
         <v>5</v>
       </c>
       <c r="D6" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E6" s="5" t="n">
         <f aca="false">IFERROR(D6/D5,0)</f>
-        <v>0.0454545454545455</v>
+        <v>0.0909090909090909</v>
       </c>
       <c r="I6" s="4" t="s">
         <v>6</v>
       </c>
       <c r="K6" s="0" t="n">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="L6" s="5" t="n">
         <f aca="false">IFERROR(K6/K5,0)</f>
-        <v>0.421259842519685</v>
+        <v>0.425196850393701</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -795,14 +795,14 @@
       </c>
       <c r="D7" s="6" t="n">
         <f aca="false">D5-D6</f>
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I7" s="4" t="s">
         <v>8</v>
       </c>
       <c r="K7" s="6" t="n">
         <f aca="false">K5-K6</f>
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -877,7 +877,7 @@
         <v>27</v>
       </c>
       <c r="C14" s="9" t="n">
-        <v>0</v>
+        <v>11159</v>
       </c>
       <c r="D14" s="9" t="n">
         <v>239895</v>
@@ -887,51 +887,51 @@
       </c>
       <c r="F14" s="10" t="n">
         <f aca="false">IFERROR(C14/E14,0)</f>
-        <v>0</v>
+        <v>0.0316567375886525</v>
       </c>
       <c r="G14" s="9" t="n">
-        <v>0</v>
+        <v>122748</v>
       </c>
       <c r="H14" s="10" t="n">
         <f aca="false">IFERROR(G14/E14,0)</f>
-        <v>0</v>
+        <v>0.348221276595745</v>
       </c>
       <c r="J14" s="9" t="n">
-        <v>0</v>
+        <v>5847</v>
       </c>
       <c r="L14" s="9" t="n">
-        <v>491054</v>
+        <v>497055</v>
       </c>
       <c r="N14" s="9" t="n">
-        <v>1172928</v>
+        <v>1184086</v>
       </c>
       <c r="O14" s="9" t="n">
         <v>1267368</v>
       </c>
       <c r="P14" s="10" t="n">
         <f aca="false">IFERROR(N14/O14,0)</f>
-        <v>0.925483363947962</v>
+        <v>0.934287436640344</v>
       </c>
       <c r="Q14" s="9" t="n">
-        <v>1474409</v>
+        <v>1488189</v>
       </c>
       <c r="R14" s="10" t="n">
         <f aca="false">IFERROR(N14/Q14,0)</f>
-        <v>0.79552417273633</v>
+        <v>0.795655659328217</v>
       </c>
       <c r="S14" s="9" t="n">
         <v>3500000</v>
       </c>
       <c r="T14" s="10" t="n">
         <f aca="false">IFERROR(N14/S14,0)</f>
-        <v>0.335122285714286</v>
+        <v>0.338310285714286</v>
       </c>
       <c r="U14" s="9" t="n">
         <v>2794760</v>
       </c>
       <c r="V14" s="10" t="n">
         <f aca="false">IFERROR(N14/U14,0)</f>
-        <v>0.419688273769483</v>
+        <v>0.423680745394953</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -939,7 +939,7 @@
         <v>28</v>
       </c>
       <c r="C15" s="9" t="n">
-        <v>2609</v>
+        <v>18280</v>
       </c>
       <c r="D15" s="9" t="n">
         <v>187602</v>
@@ -949,51 +949,51 @@
       </c>
       <c r="F15" s="10" t="n">
         <f aca="false">IFERROR(C15/E15,0)</f>
-        <v>0.0103122529644269</v>
+        <v>0.0722529644268775</v>
       </c>
       <c r="G15" s="9" t="n">
-        <v>57404</v>
+        <v>201079</v>
       </c>
       <c r="H15" s="10" t="n">
         <f aca="false">IFERROR(G15/E15,0)</f>
-        <v>0.226893280632411</v>
+        <v>0.794778656126482</v>
       </c>
       <c r="J15" s="9" t="n">
         <v>2608</v>
       </c>
       <c r="L15" s="9" t="n">
-        <v>197795</v>
+        <v>213466</v>
       </c>
       <c r="N15" s="9" t="n">
-        <v>1135437</v>
+        <v>1151107</v>
       </c>
       <c r="O15" s="9" t="n">
         <v>1200136</v>
       </c>
       <c r="P15" s="10" t="n">
         <f aca="false">IFERROR(N15/O15,0)</f>
-        <v>0.946090276435337</v>
+        <v>0.959147129991934</v>
       </c>
       <c r="Q15" s="9" t="n">
-        <v>1080953</v>
+        <v>1091055</v>
       </c>
       <c r="R15" s="10" t="n">
         <f aca="false">IFERROR(N15/Q15,0)</f>
-        <v>1.05040367157499</v>
+        <v>1.05504030502587</v>
       </c>
       <c r="S15" s="9" t="n">
         <v>2566000</v>
       </c>
       <c r="T15" s="10" t="n">
         <f aca="false">IFERROR(N15/S15,0)</f>
-        <v>0.442492985190959</v>
+        <v>0.448599766173032</v>
       </c>
       <c r="U15" s="9" t="n">
         <v>2165530</v>
       </c>
       <c r="V15" s="10" t="n">
         <f aca="false">IFERROR(N15/U15,0)</f>
-        <v>0.524322914021048</v>
+        <v>0.531559017884767</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1001,7 +1001,7 @@
         <v>29</v>
       </c>
       <c r="C16" s="9" t="n">
-        <v>1925</v>
+        <v>6758</v>
       </c>
       <c r="D16" s="9" t="n">
         <v>321418</v>
@@ -1011,51 +1011,51 @@
       </c>
       <c r="F16" s="10" t="n">
         <f aca="false">IFERROR(C16/E16,0)</f>
-        <v>0.00474137931034483</v>
+        <v>0.0166453201970443</v>
       </c>
       <c r="G16" s="9" t="n">
-        <v>42350</v>
+        <v>74335</v>
       </c>
       <c r="H16" s="10" t="n">
         <f aca="false">IFERROR(G16/E16,0)</f>
-        <v>0.104310344827586</v>
+        <v>0.183091133004926</v>
       </c>
       <c r="J16" s="9" t="n">
-        <v>0</v>
+        <v>7210</v>
       </c>
       <c r="L16" s="9" t="n">
-        <v>264011</v>
+        <v>261550</v>
       </c>
       <c r="N16" s="9" t="n">
-        <v>1633995</v>
+        <v>1638827</v>
       </c>
       <c r="O16" s="9" t="n">
         <v>2093724</v>
       </c>
       <c r="P16" s="10" t="n">
         <f aca="false">IFERROR(N16/O16,0)</f>
-        <v>0.780425213638474</v>
+        <v>0.782733063192665</v>
       </c>
       <c r="Q16" s="9" t="n">
-        <v>1904937</v>
+        <v>1922740</v>
       </c>
       <c r="R16" s="10" t="n">
         <f aca="false">IFERROR(N16/Q16,0)</f>
-        <v>0.857768524628374</v>
+        <v>0.852339369857599</v>
       </c>
       <c r="S16" s="9" t="n">
         <v>4522000</v>
       </c>
       <c r="T16" s="10" t="n">
         <f aca="false">IFERROR(N16/S16,0)</f>
-        <v>0.361343432109686</v>
+        <v>0.36241198584697</v>
       </c>
       <c r="U16" s="9" t="n">
         <v>3820751</v>
       </c>
       <c r="V16" s="10" t="n">
         <f aca="false">IFERROR(N16/U16,0)</f>
-        <v>0.427663304936647</v>
+        <v>0.428927977771909</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1099,11 +1099,11 @@
         <v>0.707489655172414</v>
       </c>
       <c r="Q17" s="9" t="n">
-        <v>471811</v>
+        <v>476220</v>
       </c>
       <c r="R17" s="10" t="n">
         <f aca="false">IFERROR(N17/Q17,0)</f>
-        <v>0.108715142292147</v>
+        <v>0.107708622065432</v>
       </c>
       <c r="S17" s="9" t="n">
         <v>1120000</v>
@@ -1125,7 +1125,7 @@
         <v>31</v>
       </c>
       <c r="C18" s="9" t="n">
-        <v>0</v>
+        <v>3065</v>
       </c>
       <c r="D18" s="9" t="n">
         <v>16997</v>
@@ -1135,51 +1135,51 @@
       </c>
       <c r="F18" s="10" t="n">
         <f aca="false">IFERROR(C18/E18,0)</f>
-        <v>0</v>
+        <v>0.0471538461538462</v>
       </c>
       <c r="G18" s="9" t="n">
-        <v>0</v>
+        <v>33715</v>
       </c>
       <c r="H18" s="10" t="n">
         <f aca="false">IFERROR(G18/E18,0)</f>
-        <v>0</v>
+        <v>0.518692307692308</v>
       </c>
       <c r="J18" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L18" s="9" t="n">
-        <v>46692</v>
+        <v>50426</v>
       </c>
       <c r="N18" s="9" t="n">
-        <v>154713</v>
+        <v>157778</v>
       </c>
       <c r="O18" s="9" t="n">
         <v>176545</v>
       </c>
       <c r="P18" s="10" t="n">
         <f aca="false">IFERROR(N18/O18,0)</f>
-        <v>0.876337477696905</v>
+        <v>0.893698490469852</v>
       </c>
       <c r="Q18" s="9" t="n">
-        <v>252756</v>
+        <v>255118</v>
       </c>
       <c r="R18" s="10" t="n">
         <f aca="false">IFERROR(N18/Q18,0)</f>
-        <v>0.612104163699378</v>
+        <v>0.61845106970108</v>
       </c>
       <c r="S18" s="9" t="n">
         <v>600000</v>
       </c>
       <c r="T18" s="10" t="n">
         <f aca="false">IFERROR(N18/S18,0)</f>
-        <v>0.257855</v>
+        <v>0.262963333333333</v>
       </c>
       <c r="U18" s="9" t="n">
         <v>322611</v>
       </c>
       <c r="V18" s="10" t="n">
         <f aca="false">IFERROR(N18/U18,0)</f>
-        <v>0.479565172917229</v>
+        <v>0.489065778910205</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1200,11 +1200,11 @@
         <v>0.00636886722009927</v>
       </c>
       <c r="G19" s="9" t="n">
-        <v>15946</v>
+        <v>7973</v>
       </c>
       <c r="H19" s="10" t="n">
         <f aca="false">IFERROR(G19/E19,0)</f>
-        <v>0.140079940264418</v>
+        <v>0.0700399701322089</v>
       </c>
       <c r="J19" s="9" t="n">
         <v>0</v>
@@ -1223,11 +1223,11 @@
         <v>2.24910566470241</v>
       </c>
       <c r="Q19" s="9" t="n">
-        <v>368457</v>
+        <v>371901</v>
       </c>
       <c r="R19" s="10" t="n">
         <f aca="false">IFERROR(N19/Q19,0)</f>
-        <v>1.05451110984457</v>
+        <v>1.04474577911864</v>
       </c>
       <c r="S19" s="9" t="n">
         <v>874656</v>
@@ -1249,7 +1249,7 @@
         <v>33</v>
       </c>
       <c r="C20" s="9" t="n">
-        <v>0</v>
+        <v>2754</v>
       </c>
       <c r="D20" s="9" t="n">
         <v>58240</v>
@@ -1259,51 +1259,51 @@
       </c>
       <c r="F20" s="10" t="n">
         <f aca="false">IFERROR(C20/E20,0)</f>
-        <v>0</v>
+        <v>0.0786857142857143</v>
       </c>
       <c r="G20" s="9" t="n">
-        <v>0</v>
+        <v>30294</v>
       </c>
       <c r="H20" s="10" t="n">
         <f aca="false">IFERROR(G20/E20,0)</f>
-        <v>0</v>
+        <v>0.865542857142857</v>
       </c>
       <c r="J20" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L20" s="9" t="n">
-        <v>0</v>
+        <v>2754</v>
       </c>
       <c r="N20" s="9" t="n">
-        <v>54345</v>
+        <v>57099</v>
       </c>
       <c r="O20" s="9" t="n">
         <v>205985</v>
       </c>
       <c r="P20" s="10" t="n">
         <f aca="false">IFERROR(N20/O20,0)</f>
-        <v>0.263829890526009</v>
+        <v>0.277199796101658</v>
       </c>
       <c r="Q20" s="9" t="n">
-        <v>252756</v>
+        <v>255118</v>
       </c>
       <c r="R20" s="10" t="n">
         <f aca="false">IFERROR(N20/Q20,0)</f>
-        <v>0.215009732706642</v>
+        <v>0.223814078191268</v>
       </c>
       <c r="S20" s="9" t="n">
         <v>600000</v>
       </c>
       <c r="T20" s="10" t="n">
         <f aca="false">IFERROR(N20/S20,0)</f>
-        <v>0.090575</v>
+        <v>0.095165</v>
       </c>
       <c r="U20" s="9" t="n">
         <v>337325</v>
       </c>
       <c r="V20" s="10" t="n">
         <f aca="false">IFERROR(N20/U20,0)</f>
-        <v>0.161105758541466</v>
+        <v>0.169269991847625</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1324,11 +1324,11 @@
         <v>0.0342454545454545</v>
       </c>
       <c r="G21" s="9" t="n">
-        <v>82874</v>
+        <v>41437</v>
       </c>
       <c r="H21" s="10" t="n">
         <f aca="false">IFERROR(G21/E21,0)</f>
-        <v>0.7534</v>
+        <v>0.3767</v>
       </c>
       <c r="J21" s="9" t="n">
         <v>0</v>
@@ -1347,11 +1347,11 @@
         <v>0.602880702277715</v>
       </c>
       <c r="Q21" s="9" t="n">
-        <v>398512</v>
+        <v>402236</v>
       </c>
       <c r="R21" s="10" t="n">
         <f aca="false">IFERROR(N21/Q21,0)</f>
-        <v>0.568013008391215</v>
+        <v>0.562754203999642</v>
       </c>
       <c r="S21" s="9" t="n">
         <v>946000</v>
@@ -1409,11 +1409,11 @@
         <v>0.673376390773406</v>
       </c>
       <c r="Q22" s="9" t="n">
-        <v>406743</v>
+        <v>410545</v>
       </c>
       <c r="R22" s="10" t="n">
         <f aca="false">IFERROR(N22/Q22,0)</f>
-        <v>0.762579810838785</v>
+        <v>0.755517665542145</v>
       </c>
       <c r="S22" s="9" t="n">
         <v>965540</v>
@@ -1435,7 +1435,7 @@
         <v>36</v>
       </c>
       <c r="C23" s="12" t="n">
-        <v>9026</v>
+        <v>46507</v>
       </c>
       <c r="D23" s="12" t="n">
         <v>930430</v>
@@ -1445,51 +1445,51 @@
       </c>
       <c r="F23" s="13" t="n">
         <f aca="false">IFERROR(C23/E23,0)</f>
-        <v>0.00622730992078222</v>
+        <v>0.0320865834794835</v>
       </c>
       <c r="G23" s="12" t="n">
-        <v>198574</v>
+        <v>511581</v>
       </c>
       <c r="H23" s="13" t="n">
         <f aca="false">IFERROR(G23/E23,0)</f>
-        <v>0.137002198117594</v>
+        <v>0.35295517799509</v>
       </c>
       <c r="J23" s="12" t="n">
-        <v>2608</v>
+        <v>15665</v>
       </c>
       <c r="L23" s="12" t="n">
-        <v>1268134</v>
+        <v>1293833</v>
       </c>
       <c r="N23" s="12" t="n">
-        <v>5127785</v>
+        <v>5165267</v>
       </c>
       <c r="O23" s="12" t="n">
         <v>6025101</v>
       </c>
       <c r="P23" s="13" t="n">
         <f aca="false">IFERROR(N23/O23,0)</f>
-        <v>0.851070380396943</v>
+        <v>0.8572913549499</v>
       </c>
       <c r="Q23" s="12" t="n">
-        <v>6611335</v>
+        <v>6673123</v>
       </c>
       <c r="R23" s="13" t="n">
         <f aca="false">IFERROR(N23/Q23,0)</f>
-        <v>0.775605078248191</v>
+        <v>0.774040430545039</v>
       </c>
       <c r="S23" s="12" t="n">
         <v>15694196</v>
       </c>
       <c r="T23" s="13" t="n">
         <f aca="false">IFERROR(N23/S23,0)</f>
-        <v>0.326731296079137</v>
+        <v>0.329119567514003</v>
       </c>
       <c r="U23" s="12" t="n">
         <v>11540927</v>
       </c>
       <c r="V23" s="13" t="n">
         <f aca="false">IFERROR(N23/U23,0)</f>
-        <v>0.44431309547318</v>
+        <v>0.447560841516457</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1745,7 +1745,7 @@
         <v>41</v>
       </c>
       <c r="C29" s="9" t="n">
-        <v>0</v>
+        <v>184</v>
       </c>
       <c r="D29" s="9" t="n">
         <v>40809</v>
@@ -1755,51 +1755,51 @@
       </c>
       <c r="F29" s="10" t="n">
         <f aca="false">IFERROR(C29/E29,0)</f>
-        <v>0</v>
+        <v>0.00736</v>
       </c>
       <c r="G29" s="9" t="n">
-        <v>0</v>
+        <v>2024</v>
       </c>
       <c r="H29" s="10" t="n">
         <f aca="false">IFERROR(G29/E29,0)</f>
-        <v>0</v>
+        <v>0.08096</v>
       </c>
       <c r="J29" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L29" s="9" t="n">
-        <v>11131</v>
+        <v>11315</v>
       </c>
       <c r="N29" s="9" t="n">
-        <v>91586</v>
+        <v>91770</v>
       </c>
       <c r="O29" s="9" t="n">
         <v>134113</v>
       </c>
       <c r="P29" s="10" t="n">
         <f aca="false">IFERROR(N29/O29,0)</f>
-        <v>0.68290173212142</v>
+        <v>0.684273709483794</v>
       </c>
       <c r="Q29" s="9" t="n">
         <v>65000</v>
       </c>
       <c r="R29" s="10" t="n">
         <f aca="false">IFERROR(N29/Q29,0)</f>
-        <v>1.40901538461538</v>
+        <v>1.41184615384615</v>
       </c>
       <c r="S29" s="9" t="n">
         <v>265000</v>
       </c>
       <c r="T29" s="10" t="n">
         <f aca="false">IFERROR(N29/S29,0)</f>
-        <v>0.345607547169811</v>
+        <v>0.346301886792453</v>
       </c>
       <c r="U29" s="9" t="n">
         <v>261659</v>
       </c>
       <c r="V29" s="10" t="n">
         <f aca="false">IFERROR(N29/U29,0)</f>
-        <v>0.350020446458941</v>
+        <v>0.350723651775785</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1807,7 +1807,7 @@
         <v>42</v>
       </c>
       <c r="C30" s="15" t="n">
-        <v>9026</v>
+        <v>46691</v>
       </c>
       <c r="D30" s="15" t="n">
         <v>979932</v>
@@ -1817,51 +1817,51 @@
       </c>
       <c r="F30" s="16" t="n">
         <f aca="false">IFERROR(C30/E30,0)</f>
-        <v>0.00610103134872944</v>
+        <v>0.0315602985490279</v>
       </c>
       <c r="G30" s="15" t="n">
-        <v>198574</v>
+        <v>513605</v>
       </c>
       <c r="H30" s="16" t="n">
         <f aca="false">IFERROR(G30/E30,0)</f>
-        <v>0.134224041551363</v>
+        <v>0.347165987797937</v>
       </c>
       <c r="J30" s="15" t="n">
-        <v>2608</v>
+        <v>15665</v>
       </c>
       <c r="L30" s="15" t="n">
-        <v>1325159</v>
+        <v>1351042</v>
       </c>
       <c r="N30" s="15" t="n">
-        <v>5342597</v>
+        <v>5380262</v>
       </c>
       <c r="O30" s="15" t="n">
         <v>6234406</v>
       </c>
       <c r="P30" s="16" t="n">
         <f aca="false">IFERROR(N30/O30,0)</f>
-        <v>0.856953653643988</v>
+        <v>0.862995127362575</v>
       </c>
       <c r="Q30" s="15" t="n">
-        <v>6691335</v>
+        <v>6753123</v>
       </c>
       <c r="R30" s="16" t="n">
         <f aca="false">IFERROR(N30/Q30,0)</f>
-        <v>0.798435140371839</v>
+        <v>0.796707241967901</v>
       </c>
       <c r="S30" s="15" t="n">
         <v>16019196</v>
       </c>
       <c r="T30" s="16" t="n">
         <f aca="false">IFERROR(N30/S30,0)</f>
-        <v>0.333512181260533</v>
+        <v>0.335863422858426</v>
       </c>
       <c r="U30" s="15" t="n">
         <v>11949524</v>
       </c>
       <c r="V30" s="16" t="n">
         <f aca="false">IFERROR(N30/U30,0)</f>
-        <v>0.447097055916202</v>
+        <v>0.450249064314194</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1915,30 +1915,30 @@
         <v>48</v>
       </c>
       <c r="C36" s="9" t="n">
-        <v>6417</v>
+        <v>44082</v>
       </c>
       <c r="E36" s="9" t="n">
         <v>922307</v>
       </c>
       <c r="F36" s="10" t="n">
         <f aca="false">IFERROR(C36/E36,0)</f>
-        <v>0.00695755317914751</v>
+        <v>0.047795365317622</v>
       </c>
       <c r="J36" s="9" t="n">
-        <v>0</v>
+        <v>10087</v>
       </c>
       <c r="K36" s="9" t="n">
         <v>1034926</v>
       </c>
       <c r="L36" s="10" t="n">
         <f aca="false">IFERROR(J36/K36,0)</f>
-        <v>0</v>
+        <v>0.00974659057749057</v>
       </c>
       <c r="N36" s="9" t="n">
-        <v>564649</v>
+        <v>592041</v>
       </c>
       <c r="P36" s="9" t="n">
-        <v>3472174</v>
+        <v>3482261</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1956,20 +1956,20 @@
         <v>0.00754886217322744</v>
       </c>
       <c r="J37" s="9" t="n">
-        <v>2608</v>
+        <v>5578</v>
       </c>
       <c r="K37" s="9" t="n">
         <v>346129</v>
       </c>
       <c r="L37" s="10" t="n">
         <f aca="false">IFERROR(J37/K37,0)</f>
-        <v>0.00753476305077009</v>
+        <v>0.0161153789483112</v>
       </c>
       <c r="N37" s="9" t="n">
-        <v>557705</v>
+        <v>556196</v>
       </c>
       <c r="P37" s="9" t="n">
-        <v>729635</v>
+        <v>732605</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2132,30 +2132,30 @@
         <v>55</v>
       </c>
       <c r="C43" s="12" t="n">
-        <v>9026</v>
+        <v>46691</v>
       </c>
       <c r="E43" s="12" t="n">
         <v>1479422</v>
       </c>
       <c r="F43" s="13" t="n">
         <f aca="false">IFERROR(C43/E43,0)</f>
-        <v>0.00610103134872944</v>
+        <v>0.0315602985490279</v>
       </c>
       <c r="J43" s="12" t="n">
-        <v>2608</v>
+        <v>15665</v>
       </c>
       <c r="K43" s="12" t="n">
         <v>1533976</v>
       </c>
       <c r="L43" s="13" t="n">
         <f aca="false">IFERROR(J43/K43,0)</f>
-        <v>0.00170015697768414</v>
+        <v>0.0102120241776925</v>
       </c>
       <c r="N43" s="12" t="n">
-        <v>1325159</v>
+        <v>1351042</v>
       </c>
       <c r="P43" s="12" t="n">
-        <v>4607857</v>
+        <v>4620914</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2173,20 +2173,20 @@
         <v>0</v>
       </c>
       <c r="J44" s="9" t="n">
-        <v>0</v>
+        <v>1716</v>
       </c>
       <c r="K44" s="9" t="n">
         <v>83162</v>
       </c>
       <c r="L44" s="10" t="n">
         <f aca="false">IFERROR(J44/K44,0)</f>
-        <v>0</v>
+        <v>0.0206344243765181</v>
       </c>
       <c r="N44" s="9" t="n">
         <v>0</v>
       </c>
       <c r="P44" s="9" t="n">
-        <v>292273</v>
+        <v>293989</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2194,7 +2194,7 @@
         <v>57</v>
       </c>
       <c r="C45" s="15" t="n">
-        <v>9026</v>
+        <v>46691</v>
       </c>
       <c r="E45" s="15" t="n">
         <v>0</v>
@@ -2204,27 +2204,27 @@
         <v>0</v>
       </c>
       <c r="J45" s="15" t="n">
-        <v>2608</v>
+        <v>17382</v>
       </c>
       <c r="K45" s="15" t="n">
         <v>1617138</v>
       </c>
       <c r="L45" s="16" t="n">
         <f aca="false">IFERROR(J45/K45,0)</f>
-        <v>0.00161272569193229</v>
+        <v>0.0107486188562757</v>
       </c>
       <c r="N45" s="15" t="n">
-        <v>1325159</v>
+        <v>1351042</v>
       </c>
       <c r="P45" s="15" t="n">
-        <v>4900130</v>
+        <v>4914903</v>
       </c>
       <c r="Q45" s="15" t="n">
         <v>6713948</v>
       </c>
       <c r="R45" s="16" t="n">
         <f aca="false">IFERROR(P45/Q45,0)</f>
-        <v>0.72984330531008</v>
+        <v>0.732043650025291</v>
       </c>
     </row>
   </sheetData>

--- a/sales_report.xlsx
+++ b/sales_report.xlsx
@@ -8,7 +8,7 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Daily Order Summary" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DASHBOARD" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -834,7 +834,6 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21"/>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
@@ -982,7 +981,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
@@ -1696,7 +1694,6 @@
       <c r="F14" t="n">
         <v>1161954</v>
       </c>
-      <c r="G14" t="inlineStr"/>
       <c r="H14" t="n">
         <v>140950</v>
       </c>
@@ -1751,11 +1748,9 @@
       <c r="D15" t="n">
         <v>0</v>
       </c>
-      <c r="E15" t="inlineStr"/>
       <c r="F15" t="n">
         <v>29896</v>
       </c>
-      <c r="G15" t="inlineStr"/>
       <c r="H15" t="n">
         <v>0</v>
       </c>
@@ -1773,11 +1768,9 @@
           <t>13%</t>
         </is>
       </c>
-      <c r="M15" t="inlineStr"/>
       <c r="N15" t="n">
         <v>0</v>
       </c>
-      <c r="O15" t="inlineStr"/>
       <c r="P15" t="n">
         <v>82466</v>
       </c>

--- a/sales_report.xlsx
+++ b/sales_report.xlsx
@@ -1736,7 +1736,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:G20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1786,64 +1786,64 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ERIC BLASKOWSKI</t>
+          <t>ELITE DEALS</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0</v>
+        <v>20883</v>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>8092</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>4558</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>11196</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>3107</v>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>47836</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>KEVIN KEITH</t>
+          <t>ERIC BLASKOWSKI</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0</v>
+        <v>172905</v>
       </c>
       <c r="C5" t="n">
-        <v>0</v>
+        <v>137415</v>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>165774</v>
       </c>
       <c r="E5" t="n">
-        <v>0</v>
+        <v>273320</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>135546</v>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>884961</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>THORNTON COLE</t>
+          <t>KCB</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>0</v>
       </c>
       <c r="C6" t="n">
-        <v>0</v>
+        <v>2084</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
@@ -1855,38 +1855,38 @@
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>2084</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>MICHAEL KUHLMAN</t>
+          <t>KEVIN KEITH</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0</v>
+        <v>184893</v>
       </c>
       <c r="C7" t="n">
-        <v>0</v>
+        <v>151654</v>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>192333</v>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
+        <v>311282</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>86191</v>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>926353</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>HAMP BRILEY</t>
+          <t>NET DIRECT</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -1896,7 +1896,7 @@
         <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>0</v>
+        <v>18017</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -1905,63 +1905,63 @@
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>18017</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>GRAYSON MOOREHEAD</t>
+          <t>THORNTON COLE</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0</v>
+        <v>291224</v>
       </c>
       <c r="C9" t="n">
-        <v>0</v>
+        <v>177307</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>342650</v>
       </c>
       <c r="E9" t="n">
-        <v>0</v>
+        <v>320793</v>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>220976</v>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>1352950</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>BEAU BOUTHILLIER</t>
+          <t>WOODLAND DIRECT</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0</v>
+        <v>25028</v>
       </c>
       <c r="C10" t="n">
-        <v>0</v>
+        <v>7558</v>
       </c>
       <c r="D10" t="n">
-        <v>0</v>
+        <v>18627</v>
       </c>
       <c r="E10" t="n">
-        <v>0</v>
+        <v>13076</v>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>10457</v>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>74746</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>SUZANNE HORST</t>
+          <t>HOUSE</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -1990,49 +1990,176 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0</v>
+        <v>44660</v>
       </c>
       <c r="C12" t="n">
-        <v>0</v>
+        <v>5262</v>
       </c>
       <c r="D12" t="n">
-        <v>0</v>
+        <v>88811</v>
       </c>
       <c r="E12" t="n">
-        <v>0</v>
+        <v>89737</v>
       </c>
       <c r="F12" t="n">
-        <v>0</v>
+        <v>4713</v>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>233183</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>SUZANNE HORST</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>66794</v>
+      </c>
+      <c r="C13" t="n">
+        <v>30664</v>
+      </c>
+      <c r="D13" t="n">
+        <v>69322</v>
+      </c>
+      <c r="E13" t="n">
+        <v>32238</v>
+      </c>
+      <c r="F13" t="n">
+        <v>42208</v>
+      </c>
+      <c r="G13" t="n">
+        <v>241226</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>MICHAEL KUHLMAN</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>15212</v>
+      </c>
+      <c r="C14" t="n">
+        <v>23667</v>
+      </c>
+      <c r="D14" t="n">
+        <v>7292</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" t="n">
+        <v>11431</v>
+      </c>
+      <c r="G14" t="n">
+        <v>57602</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>GRAYSON MOOREHEAD</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>30606</v>
+      </c>
+      <c r="C15" t="n">
+        <v>37989</v>
+      </c>
+      <c r="D15" t="n">
+        <v>46746</v>
+      </c>
+      <c r="E15" t="n">
+        <v>125490</v>
+      </c>
+      <c r="F15" t="n">
+        <v>18780</v>
+      </c>
+      <c r="G15" t="n">
+        <v>259611</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>HAMP BRILEY</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>1081</v>
+      </c>
+      <c r="C16" t="n">
+        <v>17672</v>
+      </c>
+      <c r="D16" t="n">
+        <v>28605</v>
+      </c>
+      <c r="E16" t="n">
+        <v>57050</v>
+      </c>
+      <c r="F16" t="n">
+        <v>8378</v>
+      </c>
+      <c r="G16" t="n">
+        <v>112786</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>BEAU BOUTHILLIER</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>8404</v>
+      </c>
+      <c r="C17" t="n">
+        <v>2311</v>
+      </c>
+      <c r="D17" t="n">
+        <v>5088</v>
+      </c>
+      <c r="E17" t="n">
+        <v>30087</v>
+      </c>
+      <c r="F17" t="n">
+        <v>9628</v>
+      </c>
+      <c r="G17" t="n">
+        <v>55518</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>Grand Total</t>
         </is>
       </c>
-      <c r="B13" t="n">
-        <v>0</v>
-      </c>
-      <c r="C13" t="n">
-        <v>0</v>
-      </c>
-      <c r="D13" t="n">
-        <v>0</v>
-      </c>
-      <c r="E13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0</v>
-      </c>
-      <c r="G13" t="n">
-        <v>0</v>
-      </c>
-    </row>
+      <c r="B18" t="n">
+        <v>861692</v>
+      </c>
+      <c r="C18" t="n">
+        <v>601675</v>
+      </c>
+      <c r="D18" t="n">
+        <v>987824</v>
+      </c>
+      <c r="E18" t="n">
+        <v>1264270</v>
+      </c>
+      <c r="F18" t="n">
+        <v>551414</v>
+      </c>
+      <c r="G18" t="n">
+        <v>4266874</v>
+      </c>
+    </row>
+    <row r="19"/>
+    <row r="20"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2093,7 +2220,6 @@
       <c r="D2" t="n">
         <v>848</v>
       </c>
-      <c r="E2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -2114,7 +2240,6 @@
       <c r="D3" t="n">
         <v>108</v>
       </c>
-      <c r="E3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -2135,7 +2260,6 @@
       <c r="D4" t="n">
         <v>9420</v>
       </c>
-      <c r="E4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -2156,7 +2280,6 @@
       <c r="D5" t="n">
         <v>912</v>
       </c>
-      <c r="E5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -2177,7 +2300,6 @@
       <c r="D6" t="n">
         <v>1728</v>
       </c>
-      <c r="E6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -2198,7 +2320,6 @@
       <c r="D7" t="n">
         <v>6154</v>
       </c>
-      <c r="E7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -2219,7 +2340,6 @@
       <c r="D8" t="n">
         <v>5910</v>
       </c>
-      <c r="E8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -2240,7 +2360,6 @@
       <c r="D9" t="n">
         <v>5902</v>
       </c>
-      <c r="E9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -2261,7 +2380,6 @@
       <c r="D10" t="n">
         <v>174</v>
       </c>
-      <c r="E10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -2282,7 +2400,6 @@
       <c r="D11" t="n">
         <v>0</v>
       </c>
-      <c r="E11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/sales_report.xlsx
+++ b/sales_report.xlsx
@@ -7,8 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Daily Order Summary" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DASHBOARD" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DAILY ORDER SUMMARY" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -100,7 +100,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -122,11 +122,55 @@
         <color rgb="00AAAAAA"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00AAAAAA"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00AAAAAA"/>
+      </right>
+      <top style="thin">
+        <color rgb="00AAAAAA"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00AAAAAA"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00AAAAAA"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00AAAAAA"/>
+      </right>
+      <top style="thin">
+        <color rgb="00AAAAAA"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00AAAAAA"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -188,6 +232,8 @@
     <xf numFmtId="164" fontId="7" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -581,6 +627,23 @@
           <t>FireRock Building Materials — Daily Sales &amp; Revenue Report   |   6/8/2026</t>
         </is>
       </c>
+      <c r="B1" s="21" t="n"/>
+      <c r="C1" s="21" t="n"/>
+      <c r="D1" s="21" t="n"/>
+      <c r="E1" s="21" t="n"/>
+      <c r="F1" s="21" t="n"/>
+      <c r="G1" s="21" t="n"/>
+      <c r="H1" s="21" t="n"/>
+      <c r="I1" s="21" t="n"/>
+      <c r="J1" s="21" t="n"/>
+      <c r="K1" s="21" t="n"/>
+      <c r="L1" s="21" t="n"/>
+      <c r="M1" s="21" t="n"/>
+      <c r="N1" s="21" t="n"/>
+      <c r="O1" s="21" t="n"/>
+      <c r="P1" s="21" t="n"/>
+      <c r="Q1" s="21" t="n"/>
+      <c r="R1" s="22" t="n"/>
     </row>
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
@@ -1542,6 +1605,9 @@
           <t>Sales Orders By Day   |   June 8, 2026</t>
         </is>
       </c>
+      <c r="B1" s="21" t="n"/>
+      <c r="C1" s="21" t="n"/>
+      <c r="D1" s="22" t="n"/>
     </row>
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="13" t="inlineStr">
@@ -2067,6 +2133,8 @@
           <t>GRAND TOTAL</t>
         </is>
       </c>
+      <c r="B31" s="21" t="n"/>
+      <c r="C31" s="22" t="n"/>
       <c r="D31" s="20" t="n">
         <v>61059</v>
       </c>

--- a/sales_report.xlsx
+++ b/sales_report.xlsx
@@ -23,7 +23,7 @@
     <numFmt numFmtId="165" formatCode="m/d/yyyy"/>
     <numFmt numFmtId="166" formatCode="$#,##0"/>
   </numFmts>
-  <fonts count="8">
+  <fonts count="7">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -58,10 +58,6 @@
       <name val="Arial"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <b val="1"/>
     </font>
     <font>
       <name val="Arial"/>
@@ -122,7 +118,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -170,9 +166,8 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -538,7 +533,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S30"/>
+  <dimension ref="A1:S45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -562,7 +557,7 @@
     <col width="11" customWidth="1" min="19" max="19"/>
   </cols>
   <sheetData>
-    <row r="1" ht="26" customHeight="1">
+    <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>FireRock Building Materials — Daily Sales &amp; Revenue Report</t>
@@ -621,7 +616,7 @@
         <v>0.44</v>
       </c>
     </row>
-    <row r="13" ht="24" customHeight="1">
+    <row r="13">
       <c r="B13" s="7" t="inlineStr">
         <is>
           <t>Sales Rep</t>
@@ -629,12 +624,12 @@
       </c>
       <c r="C13" s="7" t="inlineStr">
         <is>
-          <t>MTD Jun-26</t>
+          <t>MTD</t>
         </is>
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
-          <t>MTD Jun-25</t>
+          <t>PY</t>
         </is>
       </c>
       <c r="E13" s="7" t="inlineStr">
@@ -697,7 +692,7 @@
         <v>0.2</v>
       </c>
       <c r="G14" s="9" t="n">
-        <v>353990</v>
+        <v>253990</v>
       </c>
       <c r="H14" s="10" t="n">
         <v>0.72</v>
@@ -1018,25 +1013,25 @@
         </is>
       </c>
       <c r="C23" s="13" t="n">
-        <v>301720</v>
+        <v>301721</v>
       </c>
       <c r="D23" s="13" t="n">
-        <v>930430</v>
+        <v>930429</v>
       </c>
       <c r="E23" s="13" t="n">
         <v>1449422</v>
       </c>
       <c r="F23" s="14" t="n">
-        <v>0.21</v>
+        <v>0.2081664277208432</v>
       </c>
       <c r="G23" s="13" t="n">
-        <v>1106307</v>
+        <v>1106308</v>
       </c>
       <c r="H23" s="14" t="n">
-        <v>0.76</v>
+        <v>0.7632752918059751</v>
       </c>
       <c r="L23" s="13" t="n">
-        <v>247107</v>
+        <v>247108</v>
       </c>
       <c r="N23" s="13" t="n">
         <v>5421774</v>
@@ -1055,25 +1050,25 @@
         </is>
       </c>
       <c r="C30" s="13" t="n">
-        <v>301720</v>
+        <v>301721</v>
       </c>
       <c r="D30" s="13" t="n">
-        <v>930430</v>
+        <v>930429</v>
       </c>
       <c r="E30" s="13" t="n">
         <v>1449422</v>
       </c>
       <c r="F30" s="14" t="n">
-        <v>0.21</v>
+        <v>0.2081664277208432</v>
       </c>
       <c r="G30" s="13" t="n">
-        <v>1106307</v>
+        <v>1106308</v>
       </c>
       <c r="H30" s="14" t="n">
-        <v>0.76</v>
+        <v>0.7632752918059751</v>
       </c>
       <c r="L30" s="13" t="n">
-        <v>247107</v>
+        <v>247108</v>
       </c>
       <c r="N30" s="13" t="n">
         <v>5421774</v>
@@ -1083,6 +1078,283 @@
       </c>
       <c r="S30" s="13" t="n">
         <v>15694196</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>FIREPLACE/PP</t>
+        </is>
+      </c>
+      <c r="C36" s="11" t="n">
+        <v>266557</v>
+      </c>
+      <c r="E36" s="11" t="n">
+        <v>922307</v>
+      </c>
+      <c r="F36" s="6" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="J36" s="11" t="n">
+        <v>180320</v>
+      </c>
+      <c r="K36" s="11" t="n">
+        <v>1034926</v>
+      </c>
+      <c r="L36" s="6" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="N36" s="11" t="n">
+        <v>624233</v>
+      </c>
+      <c r="P36" s="11" t="n">
+        <v>3652844</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>PAVER/PP</t>
+        </is>
+      </c>
+      <c r="C37" s="11" t="n">
+        <v>32338</v>
+      </c>
+      <c r="E37" s="11" t="n">
+        <v>345615</v>
+      </c>
+      <c r="F37" s="6" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="J37" s="11" t="n">
+        <v>52672</v>
+      </c>
+      <c r="K37" s="11" t="n">
+        <v>346129</v>
+      </c>
+      <c r="L37" s="6" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="N37" s="11" t="n">
+        <v>558558</v>
+      </c>
+      <c r="P37" s="11" t="n">
+        <v>779699</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>ROOFING</t>
+        </is>
+      </c>
+      <c r="C38" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E38" s="11" t="n">
+        <v>54500</v>
+      </c>
+      <c r="F38" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J38" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K38" s="11" t="n">
+        <v>24961</v>
+      </c>
+      <c r="L38" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N38" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P38" s="11" t="n">
+        <v>32032</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>FLOORING</t>
+        </is>
+      </c>
+      <c r="C39" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E39" s="11" t="n">
+        <v>57000</v>
+      </c>
+      <c r="F39" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J39" s="11" t="n">
+        <v>2475</v>
+      </c>
+      <c r="K39" s="11" t="n">
+        <v>27961</v>
+      </c>
+      <c r="L39" s="6" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="N39" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P39" s="11" t="n">
+        <v>133112</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>INSTALLATION</t>
+        </is>
+      </c>
+      <c r="C40" s="11" t="n">
+        <v>12495</v>
+      </c>
+      <c r="E40" s="11" t="n">
+        <v>100000</v>
+      </c>
+      <c r="F40" s="6" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="J40" s="11" t="n">
+        <v>21656</v>
+      </c>
+      <c r="K40" s="11" t="n">
+        <v>99999</v>
+      </c>
+      <c r="L40" s="6" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="N40" s="11" t="n">
+        <v>177100</v>
+      </c>
+      <c r="P40" s="11" t="n">
+        <v>265034</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>SWD</t>
+        </is>
+      </c>
+      <c r="C41" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E41" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F41" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J41" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K41" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L41" s="6" t="n">
+        <v>16544</v>
+      </c>
+      <c r="N41" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P41" s="11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="C42" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E42" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F42" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J42" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K42" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L42" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N42" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P42" s="11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="C43" s="11" t="n">
+        <v>311390</v>
+      </c>
+      <c r="J43" s="11" t="n">
+        <v>257123</v>
+      </c>
+      <c r="N43" s="11" t="n">
+        <v>1359891</v>
+      </c>
+      <c r="P43" s="11" t="n">
+        <v>4862721</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>FREIGHT</t>
+        </is>
+      </c>
+      <c r="J44" s="11" t="n">
+        <v>14028</v>
+      </c>
+      <c r="P44" s="11" t="n">
+        <v>306301</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>TOTAL W/ FREIGHT</t>
+        </is>
+      </c>
+      <c r="C45" s="11" t="n">
+        <v>311390</v>
+      </c>
+      <c r="J45" s="11" t="n">
+        <v>271151</v>
+      </c>
+      <c r="K45" s="11" t="n">
+        <v>1617138</v>
+      </c>
+      <c r="L45" s="6" t="n">
+        <v>0.1676733834712931</v>
+      </c>
+      <c r="P45" s="11" t="n">
+        <v>5169022</v>
+      </c>
+      <c r="Q45" s="11" t="n">
+        <v>6713948</v>
+      </c>
+      <c r="R45" s="6" t="n">
+        <v>0.7698930644086013</v>
       </c>
     </row>
   </sheetData>
@@ -1099,72 +1371,406 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A3:G20"/>
+  <dimension ref="A4:G19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
   </cols>
   <sheetData>
-    <row r="3">
-      <c r="A3" s="15" t="inlineStr">
+    <row r="4">
+      <c r="A4" s="15" t="inlineStr">
         <is>
           <t>SALES REP</t>
         </is>
       </c>
-      <c r="B3" s="15" t="inlineStr">
+      <c r="B4" s="15" t="inlineStr">
         <is>
           <t>Jan</t>
         </is>
       </c>
-      <c r="C3" s="15" t="inlineStr">
+      <c r="C4" s="15" t="inlineStr">
         <is>
           <t>Feb</t>
         </is>
       </c>
-      <c r="D3" s="15" t="inlineStr">
+      <c r="D4" s="15" t="inlineStr">
         <is>
           <t>Mar</t>
         </is>
       </c>
-      <c r="E3" s="15" t="inlineStr">
+      <c r="E4" s="15" t="inlineStr">
         <is>
           <t>Apr</t>
         </is>
       </c>
-      <c r="F3" s="15" t="inlineStr">
+      <c r="F4" s="15" t="inlineStr">
         <is>
           <t>May</t>
         </is>
       </c>
-      <c r="G3" s="15" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="16" t="inlineStr">
+      <c r="G4" s="15" t="inlineStr">
         <is>
           <t>Grand Total</t>
         </is>
       </c>
-      <c r="B20" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="C20" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="D20" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="E20" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="F20" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="G20" s="17" t="n">
-        <v>0</v>
+    </row>
+    <row r="5">
+      <c r="A5" s="16" t="inlineStr">
+        <is>
+          <t>ELITE DEALS</t>
+        </is>
+      </c>
+      <c r="B5" s="17" t="n">
+        <v>20883.4</v>
+      </c>
+      <c r="C5" s="17" t="n">
+        <v>8092.18</v>
+      </c>
+      <c r="D5" s="17" t="n">
+        <v>4557.53</v>
+      </c>
+      <c r="E5" s="17" t="n">
+        <v>11196.48</v>
+      </c>
+      <c r="F5" s="17" t="n">
+        <v>3106.62</v>
+      </c>
+      <c r="G5" s="17" t="n">
+        <v>47836.21000000001</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="16" t="inlineStr">
+        <is>
+          <t>ERIC BLASKOWSKI</t>
+        </is>
+      </c>
+      <c r="B6" s="17" t="n">
+        <v>172905.2999999999</v>
+      </c>
+      <c r="C6" s="17" t="n">
+        <v>137414.86</v>
+      </c>
+      <c r="D6" s="17" t="n">
+        <v>165774.44</v>
+      </c>
+      <c r="E6" s="17" t="n">
+        <v>273320.11</v>
+      </c>
+      <c r="F6" s="17" t="n">
+        <v>135546.3</v>
+      </c>
+      <c r="G6" s="17" t="n">
+        <v>884961.01</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="16" t="inlineStr">
+        <is>
+          <t>KCB</t>
+        </is>
+      </c>
+      <c r="B7" s="17" t="n"/>
+      <c r="C7" s="17" t="n">
+        <v>2084</v>
+      </c>
+      <c r="D7" s="17" t="n"/>
+      <c r="E7" s="17" t="n"/>
+      <c r="F7" s="17" t="n"/>
+      <c r="G7" s="17" t="n">
+        <v>2084</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="16" t="inlineStr">
+        <is>
+          <t>KEVIN KEITH</t>
+        </is>
+      </c>
+      <c r="B8" s="17" t="n">
+        <v>184892.87</v>
+      </c>
+      <c r="C8" s="17" t="n">
+        <v>151654.09</v>
+      </c>
+      <c r="D8" s="17" t="n">
+        <v>192332.91</v>
+      </c>
+      <c r="E8" s="17" t="n">
+        <v>311281.82</v>
+      </c>
+      <c r="F8" s="17" t="n">
+        <v>86191.32999999996</v>
+      </c>
+      <c r="G8" s="17" t="n">
+        <v>926353.0199999999</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="16" t="inlineStr">
+        <is>
+          <t>NET DIRECT</t>
+        </is>
+      </c>
+      <c r="B9" s="17" t="n"/>
+      <c r="C9" s="17" t="n"/>
+      <c r="D9" s="17" t="n">
+        <v>18017.34</v>
+      </c>
+      <c r="E9" s="17" t="n"/>
+      <c r="F9" s="17" t="n"/>
+      <c r="G9" s="17" t="n">
+        <v>18017.34</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="16" t="inlineStr">
+        <is>
+          <t>THORNTON COLE</t>
+        </is>
+      </c>
+      <c r="B10" s="17" t="n">
+        <v>291224.3699999999</v>
+      </c>
+      <c r="C10" s="17" t="n">
+        <v>177306.69</v>
+      </c>
+      <c r="D10" s="17" t="n">
+        <v>342650.01</v>
+      </c>
+      <c r="E10" s="17" t="n">
+        <v>320793.4400000001</v>
+      </c>
+      <c r="F10" s="17" t="n">
+        <v>220975.64</v>
+      </c>
+      <c r="G10" s="17" t="n">
+        <v>1352950.15</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="16" t="inlineStr">
+        <is>
+          <t>WOODLAND DIRECT</t>
+        </is>
+      </c>
+      <c r="B11" s="17" t="n">
+        <v>25027.94</v>
+      </c>
+      <c r="C11" s="17" t="n">
+        <v>7557.52</v>
+      </c>
+      <c r="D11" s="17" t="n">
+        <v>18627.35</v>
+      </c>
+      <c r="E11" s="17" t="n">
+        <v>13076</v>
+      </c>
+      <c r="F11" s="17" t="n">
+        <v>10456.56</v>
+      </c>
+      <c r="G11" s="17" t="n">
+        <v>74745.37</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="16" t="inlineStr">
+        <is>
+          <t>HOUSE</t>
+        </is>
+      </c>
+      <c r="B12" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="C12" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" s="17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="16" t="inlineStr">
+        <is>
+          <t>TIFFANY HASEKER</t>
+        </is>
+      </c>
+      <c r="B13" s="17" t="n">
+        <v>44660.09</v>
+      </c>
+      <c r="C13" s="17" t="n">
+        <v>5262.04</v>
+      </c>
+      <c r="D13" s="17" t="n">
+        <v>88811.11</v>
+      </c>
+      <c r="E13" s="17" t="n">
+        <v>89737.33</v>
+      </c>
+      <c r="F13" s="17" t="n">
+        <v>4712.620000000001</v>
+      </c>
+      <c r="G13" s="17" t="n">
+        <v>233183.19</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="16" t="inlineStr">
+        <is>
+          <t>SUZANNE HORST</t>
+        </is>
+      </c>
+      <c r="B14" s="17" t="n">
+        <v>66794.44</v>
+      </c>
+      <c r="C14" s="17" t="n">
+        <v>30664.01</v>
+      </c>
+      <c r="D14" s="17" t="n">
+        <v>69322.32999999999</v>
+      </c>
+      <c r="E14" s="17" t="n">
+        <v>32238.09</v>
+      </c>
+      <c r="F14" s="17" t="n">
+        <v>42207.69</v>
+      </c>
+      <c r="G14" s="17" t="n">
+        <v>241226.56</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="16" t="inlineStr">
+        <is>
+          <t>MICHAEL KUHLMAN</t>
+        </is>
+      </c>
+      <c r="B15" s="17" t="n">
+        <v>15212.41</v>
+      </c>
+      <c r="C15" s="17" t="n">
+        <v>23667.3</v>
+      </c>
+      <c r="D15" s="17" t="n">
+        <v>7292.070000000001</v>
+      </c>
+      <c r="E15" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" s="17" t="n">
+        <v>11430.6</v>
+      </c>
+      <c r="G15" s="17" t="n">
+        <v>57602.38</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="16" t="inlineStr">
+        <is>
+          <t>GRAY MOOREHEAD</t>
+        </is>
+      </c>
+      <c r="B16" s="17" t="n">
+        <v>30605.95</v>
+      </c>
+      <c r="C16" s="17" t="n">
+        <v>37989.4</v>
+      </c>
+      <c r="D16" s="17" t="n">
+        <v>46745.63000000001</v>
+      </c>
+      <c r="E16" s="17" t="n">
+        <v>125489.73</v>
+      </c>
+      <c r="F16" s="17" t="n">
+        <v>18780.32</v>
+      </c>
+      <c r="G16" s="17" t="n">
+        <v>259611.03</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="16" t="inlineStr">
+        <is>
+          <t>HAMP BRILEY</t>
+        </is>
+      </c>
+      <c r="B17" s="17" t="n">
+        <v>1081</v>
+      </c>
+      <c r="C17" s="17" t="n">
+        <v>17671.98</v>
+      </c>
+      <c r="D17" s="17" t="n">
+        <v>28605.25999999999</v>
+      </c>
+      <c r="E17" s="17" t="n">
+        <v>57049.81999999999</v>
+      </c>
+      <c r="F17" s="17" t="n">
+        <v>8377.780000000001</v>
+      </c>
+      <c r="G17" s="17" t="n">
+        <v>112785.84</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="16" t="inlineStr">
+        <is>
+          <t>BEAU BOUTHILLIER</t>
+        </is>
+      </c>
+      <c r="B18" s="17" t="n">
+        <v>8403.85</v>
+      </c>
+      <c r="C18" s="17" t="n">
+        <v>2311.2</v>
+      </c>
+      <c r="D18" s="17" t="n">
+        <v>5087.52</v>
+      </c>
+      <c r="E18" s="17" t="n">
+        <v>30087.2</v>
+      </c>
+      <c r="F18" s="17" t="n">
+        <v>9628.32</v>
+      </c>
+      <c r="G18" s="17" t="n">
+        <v>55518.09</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="16" t="inlineStr">
+        <is>
+          <t>Grand Total</t>
+        </is>
+      </c>
+      <c r="B19" s="17" t="n">
+        <v>861691.6199999999</v>
+      </c>
+      <c r="C19" s="17" t="n">
+        <v>601675.27</v>
+      </c>
+      <c r="D19" s="17" t="n">
+        <v>987823.5</v>
+      </c>
+      <c r="E19" s="17" t="n">
+        <v>1264270.02</v>
+      </c>
+      <c r="F19" s="17" t="n">
+        <v>551413.7799999998</v>
+      </c>
+      <c r="G19" s="17" t="n">
+        <v>4266874.189999999</v>
       </c>
     </row>
   </sheetData>
@@ -1183,7 +1789,7 @@
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="36" customWidth="1" min="3" max="3"/>
+    <col width="38" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
@@ -1215,424 +1821,404 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="18" t="inlineStr">
+      <c r="A2" s="16" t="inlineStr">
         <is>
           <t>THORNTON COLE</t>
         </is>
       </c>
-      <c r="B2" s="18" t="inlineStr">
+      <c r="B2" s="16" t="inlineStr">
         <is>
           <t>FRKO150376</t>
         </is>
       </c>
-      <c r="C2" s="18" t="inlineStr">
+      <c r="C2" s="16" t="inlineStr">
         <is>
           <t>MAGNOLIA CLAY PRODUCTS</t>
         </is>
       </c>
-      <c r="D2" s="19" t="n">
+      <c r="D2" s="18" t="n">
         <v>4195</v>
       </c>
-      <c r="E2" s="18" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="18" t="inlineStr">
+      <c r="A3" s="16" t="inlineStr">
         <is>
           <t>THORNTON COLE</t>
         </is>
       </c>
-      <c r="B3" s="18" t="inlineStr">
+      <c r="B3" s="16" t="inlineStr">
         <is>
           <t>FRKO150470</t>
         </is>
       </c>
-      <c r="C3" s="18" t="inlineStr">
+      <c r="C3" s="16" t="inlineStr">
         <is>
           <t>JENNINGS BUILDERS SUPPLY - CASHIERS</t>
         </is>
       </c>
-      <c r="D3" s="19" t="n">
+      <c r="D3" s="18" t="n">
         <v>16084</v>
       </c>
-      <c r="E3" s="18" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="18" t="inlineStr">
+      <c r="A4" s="16" t="inlineStr">
         <is>
           <t>THORNTON COLE</t>
         </is>
       </c>
-      <c r="B4" s="18" t="inlineStr">
+      <c r="B4" s="16" t="inlineStr">
         <is>
           <t>FRKO150489</t>
         </is>
       </c>
-      <c r="C4" s="18" t="inlineStr">
+      <c r="C4" s="16" t="inlineStr">
         <is>
           <t>OLD SOUTH BRICK &amp; SUPPLY</t>
         </is>
       </c>
-      <c r="D4" s="19" t="n">
+      <c r="D4" s="18" t="n">
         <v>4161</v>
       </c>
-      <c r="E4" s="18" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="18" t="inlineStr">
+      <c r="A5" s="16" t="inlineStr">
         <is>
           <t>THORNTON COLE</t>
         </is>
       </c>
-      <c r="B5" s="18" t="inlineStr">
+      <c r="B5" s="16" t="inlineStr">
         <is>
           <t>FRKO150494</t>
         </is>
       </c>
-      <c r="C5" s="18" t="inlineStr">
+      <c r="C5" s="16" t="inlineStr">
         <is>
           <t>CHRISTIE CUT - MEMPHIS</t>
         </is>
       </c>
-      <c r="D5" s="19" t="n">
+      <c r="D5" s="18" t="n">
         <v>1775</v>
       </c>
-      <c r="E5" s="18" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="18" t="inlineStr">
+      <c r="A6" s="16" t="inlineStr">
         <is>
           <t>THORNTON COLE</t>
         </is>
       </c>
-      <c r="B6" s="18" t="inlineStr">
+      <c r="B6" s="16" t="inlineStr">
         <is>
           <t>FRKO150496</t>
         </is>
       </c>
-      <c r="C6" s="18" t="inlineStr">
+      <c r="C6" s="16" t="inlineStr">
         <is>
           <t>METRO BRICK &amp; STONE</t>
         </is>
       </c>
-      <c r="D6" s="19" t="n">
+      <c r="D6" s="18" t="n">
         <v>13434</v>
       </c>
-      <c r="E6" s="18" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="18" t="inlineStr">
+      <c r="A7" s="16" t="inlineStr">
         <is>
           <t>THORNTON COLE</t>
         </is>
       </c>
-      <c r="B7" s="18" t="inlineStr">
+      <c r="B7" s="16" t="inlineStr">
         <is>
           <t>FRKO150503</t>
         </is>
       </c>
-      <c r="C7" s="18" t="inlineStr">
+      <c r="C7" s="16" t="inlineStr">
         <is>
           <t>CHRISTIE CUT - MEMPHIS</t>
         </is>
       </c>
-      <c r="D7" s="19" t="n">
+      <c r="D7" s="18" t="n">
         <v>4666</v>
       </c>
-      <c r="E7" s="18" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="18" t="inlineStr">
+      <c r="A8" s="16" t="inlineStr">
         <is>
           <t>THORNTON COLE</t>
         </is>
       </c>
-      <c r="B8" s="18" t="inlineStr">
+      <c r="B8" s="16" t="inlineStr">
         <is>
           <t>FRKO150505</t>
         </is>
       </c>
-      <c r="C8" s="18" t="inlineStr">
+      <c r="C8" s="16" t="inlineStr">
         <is>
           <t>COCREHAM BRICK &amp; STONE</t>
         </is>
       </c>
-      <c r="D8" s="19" t="n">
+      <c r="D8" s="18" t="n">
         <v>1940</v>
       </c>
-      <c r="E8" s="18" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="18" t="inlineStr">
+      <c r="A9" s="16" t="inlineStr">
         <is>
           <t>SUZANNE HORST</t>
         </is>
       </c>
-      <c r="B9" s="18" t="inlineStr">
+      <c r="B9" s="16" t="inlineStr">
         <is>
           <t>FRKO150501</t>
         </is>
       </c>
-      <c r="C9" s="18" t="inlineStr">
+      <c r="C9" s="16" t="inlineStr">
         <is>
           <t>B&amp;L DISTRIBUTING CO</t>
         </is>
       </c>
-      <c r="D9" s="19" t="n">
+      <c r="D9" s="18" t="n">
         <v>357</v>
       </c>
-      <c r="E9" s="18" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="18" t="inlineStr">
+      <c r="A10" s="16" t="inlineStr">
         <is>
           <t>SUZANNE HORST</t>
         </is>
       </c>
-      <c r="B10" s="18" t="inlineStr">
+      <c r="B10" s="16" t="inlineStr">
         <is>
           <t>FRKO150504</t>
         </is>
       </c>
-      <c r="C10" s="18" t="inlineStr">
+      <c r="C10" s="16" t="inlineStr">
         <is>
           <t>DANE CONSTRUCTION SERVICES</t>
         </is>
       </c>
-      <c r="D10" s="19" t="n">
+      <c r="D10" s="18" t="n">
         <v>4788</v>
       </c>
-      <c r="E10" s="18" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="18" t="inlineStr">
+      <c r="A11" s="16" t="inlineStr">
         <is>
           <t>KEVIN KEITH</t>
         </is>
       </c>
-      <c r="B11" s="18" t="inlineStr">
+      <c r="B11" s="16" t="inlineStr">
         <is>
           <t>FRKO150407-P</t>
         </is>
       </c>
-      <c r="C11" s="18" t="inlineStr">
+      <c r="C11" s="16" t="inlineStr">
         <is>
           <t>WHATLEY SUPPLY COMPANY</t>
         </is>
       </c>
-      <c r="D11" s="19" t="n">
+      <c r="D11" s="18" t="n">
         <v>522</v>
       </c>
-      <c r="E11" s="18" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="18" t="inlineStr">
+      <c r="A12" s="16" t="inlineStr">
         <is>
           <t>KEVIN KEITH</t>
         </is>
       </c>
-      <c r="B12" s="18" t="inlineStr">
+      <c r="B12" s="16" t="inlineStr">
         <is>
           <t>FRKO150492</t>
         </is>
       </c>
-      <c r="C12" s="18" t="inlineStr">
+      <c r="C12" s="16" t="inlineStr">
         <is>
           <t>Creative Habitats</t>
         </is>
       </c>
-      <c r="D12" s="19" t="n">
+      <c r="D12" s="18" t="n">
         <v>2800</v>
       </c>
-      <c r="E12" s="18" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="18" t="inlineStr">
+      <c r="A13" s="16" t="inlineStr">
         <is>
           <t>KEVIN KEITH</t>
         </is>
       </c>
-      <c r="B13" s="18" t="inlineStr">
+      <c r="B13" s="16" t="inlineStr">
         <is>
           <t>FRKO150493-P</t>
         </is>
       </c>
-      <c r="C13" s="18" t="inlineStr">
+      <c r="C13" s="16" t="inlineStr">
         <is>
           <t>PLATINUM OUTDOOR CONSTRUCTION</t>
         </is>
       </c>
-      <c r="D13" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E13" s="18" t="inlineStr"/>
+      <c r="D13" s="18" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
-      <c r="A14" s="18" t="inlineStr">
+      <c r="A14" s="16" t="inlineStr">
         <is>
           <t>TIFFANY HASEKER</t>
         </is>
       </c>
-      <c r="B14" s="18" t="inlineStr">
+      <c r="B14" s="16" t="inlineStr">
         <is>
           <t>FRKO150182-P</t>
         </is>
       </c>
-      <c r="C14" s="18" t="inlineStr">
+      <c r="C14" s="16" t="inlineStr">
         <is>
           <t>NORTH BAY BRICK</t>
         </is>
       </c>
-      <c r="D14" s="19" t="n">
+      <c r="D14" s="18" t="n">
         <v>2189</v>
       </c>
-      <c r="E14" s="18" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="18" t="inlineStr">
+      <c r="A15" s="16" t="inlineStr">
         <is>
           <t>TIFFANY HASEKER</t>
         </is>
       </c>
-      <c r="B15" s="18" t="inlineStr">
+      <c r="B15" s="16" t="inlineStr">
         <is>
           <t>FRKO150502</t>
         </is>
       </c>
-      <c r="C15" s="18" t="inlineStr">
+      <c r="C15" s="16" t="inlineStr">
         <is>
           <t>WR TAYLOR &amp; COMPANY</t>
         </is>
       </c>
-      <c r="D15" s="19" t="n">
+      <c r="D15" s="18" t="n">
         <v>244</v>
       </c>
-      <c r="E15" s="18" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="18" t="inlineStr">
+      <c r="A16" s="16" t="inlineStr">
         <is>
           <t>GRAY MOOREHEAD</t>
         </is>
       </c>
-      <c r="B16" s="18" t="inlineStr">
+      <c r="B16" s="16" t="inlineStr">
         <is>
           <t>FRKO150497-P</t>
         </is>
       </c>
-      <c r="C16" s="18" t="inlineStr">
+      <c r="C16" s="16" t="inlineStr">
         <is>
           <t>SCP - NASHVILLE</t>
         </is>
       </c>
-      <c r="D16" s="19" t="n">
+      <c r="D16" s="18" t="n">
         <v>1860</v>
       </c>
-      <c r="E16" s="18" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="18" t="inlineStr">
+      <c r="A17" s="16" t="inlineStr">
         <is>
           <t>GRAY MOOREHEAD</t>
         </is>
       </c>
-      <c r="B17" s="18" t="inlineStr">
+      <c r="B17" s="16" t="inlineStr">
         <is>
           <t>FRKO150499</t>
         </is>
       </c>
-      <c r="C17" s="18" t="inlineStr">
+      <c r="C17" s="16" t="inlineStr">
         <is>
           <t>WILLOW WINDOW</t>
         </is>
       </c>
-      <c r="D17" s="19" t="n">
+      <c r="D17" s="18" t="n">
         <v>460</v>
       </c>
-      <c r="E17" s="18" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="18" t="inlineStr">
+      <c r="A18" s="16" t="inlineStr">
         <is>
           <t>ELITE DEALS</t>
         </is>
       </c>
-      <c r="B18" s="18" t="inlineStr">
+      <c r="B18" s="16" t="inlineStr">
         <is>
           <t>FRKO150509</t>
         </is>
       </c>
-      <c r="C18" s="18" t="inlineStr">
+      <c r="C18" s="16" t="inlineStr">
         <is>
           <t>ELITE DEALS LLC</t>
         </is>
       </c>
-      <c r="D18" s="19" t="n">
+      <c r="D18" s="18" t="n">
         <v>1584</v>
       </c>
-      <c r="E18" s="18" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="18" t="inlineStr">
+      <c r="A19" s="16" t="inlineStr">
         <is>
           <t>BEAU BOUTHILLIER</t>
         </is>
       </c>
-      <c r="B19" s="18" t="inlineStr">
+      <c r="B19" s="16" t="inlineStr">
         <is>
           <t>FRKO150490</t>
         </is>
       </c>
-      <c r="C19" s="18" t="inlineStr">
+      <c r="C19" s="16" t="inlineStr">
         <is>
           <t>POSITIVE CHIMNEY &amp; FIRE PLACE</t>
         </is>
       </c>
-      <c r="D19" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E19" s="18" t="inlineStr"/>
+      <c r="D19" s="18" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
-      <c r="A20" s="18" t="inlineStr">
+      <c r="A20" s="16" t="inlineStr">
         <is>
           <t>HOUSE</t>
         </is>
       </c>
-      <c r="B20" s="18" t="inlineStr">
+      <c r="B20" s="16" t="inlineStr">
         <is>
           <t>FRKO150491-P</t>
         </is>
       </c>
-      <c r="C20" s="18" t="inlineStr">
+      <c r="C20" s="16" t="inlineStr">
         <is>
           <t>PAVER SAMPLES</t>
         </is>
       </c>
-      <c r="D20" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E20" s="18" t="inlineStr"/>
+      <c r="D20" s="18" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
-      <c r="A21" s="18" t="inlineStr">
+      <c r="A21" s="16" t="inlineStr">
         <is>
           <t>HOUSE</t>
         </is>
       </c>
-      <c r="B21" s="18" t="inlineStr">
+      <c r="B21" s="16" t="inlineStr">
         <is>
           <t>FRKO150506-P</t>
         </is>
       </c>
-      <c r="C21" s="18" t="inlineStr">
+      <c r="C21" s="16" t="inlineStr">
         <is>
           <t>PAVER DISPLAYS</t>
         </is>
       </c>
-      <c r="D21" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E21" s="18" t="inlineStr"/>
+      <c r="D21" s="18" t="n">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
